--- a/deepseek_v3_ops.xlsx
+++ b/deepseek_v3_ops.xlsx
@@ -8,12 +8,15 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model Config" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operator Sequence" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Layer" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fused Operators" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw Operator Sequence" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Layer" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fusion Rules" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Operator Sequence'!$A$1:$I$401</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fused Operators'!$A$1:$K$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Raw Operator Sequence'!$A$1:$I$401</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -40,7 +43,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +72,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E3F2FD"/>
         <bgColor rgb="00E3F2FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -113,20 +122,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -151,6 +160,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -786,6 +799,4042 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K76"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Fused Operator</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Constituent Aten Ops</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Sub-ops</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Fused Input Shapes</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Fused Input Dtypes</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Input Sources</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Fused Output Shapes</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Fused Output Dtypes</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Output Sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>model (DeepseekV3Model)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>aten.embedding.default → aten.rsub.Scalar → aten._to_copy.default → aten.masked_fill.Scalar</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>[129280, 7168], [1, 128], [1, 1, 128, 128]</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.int64, torch.float32</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>aten.embedding.default (in[0]) | aten.embedding.default (in[1]) | aten.rsub.Scalar (in[0])</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168], [1, 1, 128, 128]</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>aten.embedding.default (out[0]) | aten.masked_fill.Scalar (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>input_layernorm (DeepseekV3RMSNorm)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar → aten.mean.dim → aten.add.Tensor → aten.rsqrt.default → aten.mul.Tensor</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168], [7168]</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar (in[0]) | aten.mul.Tensor (in[0])</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168]</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.q_a_proj</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>[128, 7168], [7168, 1536]</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (in[0]) | aten.mm.default (in[1])</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>[128, 1536]</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.q_a_layernorm (DeepseekV3RMSNorm)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar → aten.mean.dim → aten.add.Tensor → aten.rsqrt.default → aten.mul.Tensor</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 1536], [1536]</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar (in[0]) | aten.mul.Tensor (in[0])</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 1536]</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.q_b_proj</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>[128, 1536], [1536, 24576]</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (in[0]) | aten.mm.default (in[1])</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>[128, 24576]</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>self_attn</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 128, 192]</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int (in[0])</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 128, 192]</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.kv_a_proj_with_mqa</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>[128, 7168], [7168, 576]</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (in[0]) | aten.mm.default (in[1])</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>[128, 576]</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>self_attn</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 1, 64]</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int (in[0])</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>[1, 1, 128, 64]</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.kv_a_layernorm (DeepseekV3RMSNorm)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar → aten.mean.dim → aten.add.Tensor → aten.rsqrt.default → aten.mul.Tensor</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 512], [512]</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar (in[0]) | aten.mul.Tensor (in[0])</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 512]</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.kv_b_proj</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>[128, 512], [512, 32768]</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (in[0]) | aten.mm.default (in[1])</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>[128, 32768]</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>self_attn</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 128, 256]</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int (in[0])</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 128, 256]</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.rotary_emb (DeepseekV3YarnRotaryEmbedding)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>aten.arange.start_step → aten.div.Tensor → aten.pow.Scalar → aten.reciprocal.default → aten.mul.Tensor → aten.sub.Tensor → aten.clamp.default → aten._to_copy.default → aten.rsub.Scalar → aten.add.Tensor → aten.cat.default → aten.cos.default → aten.sin.default</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>[128, 1]</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor (in[0])</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>[128, 64], [128, 64]</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor (out[0]) | aten.mul.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>self_attn (DeepseekV3Attention)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>aten.index.Tensor → aten.transpose.int → aten.mul.Tensor → aten.neg.default → aten.cat.default → aten.add.Tensor → aten.new_empty.default → aten.copy_.default → aten.bmm.default → aten._softmax.default</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>[128, 64], [1, 128], [128, 64], [1, 128, 128, 64], [1, 1, 128, 64], [1, 128, 128, 32], [1, 128, 128, 32], [1, 1, 128, 64], [1, 1, 128, 32], [1, 1, 128, 32], [1, 128, 128, 128], [1, 128, 128, 128], [1, 128, 128, 64], [1, 128, 128, 128], [1, 1, 128, 128], [128, 128, 128], [1, 128, 128, 128]</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.int64, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>aten.index.Tensor (in[0]) | aten.index.Tensor (in[1]) | aten.index.Tensor (in[0]) | aten.mul.Tensor (in[0]) | aten.mul.Tensor (in[1]) | aten.neg.default (in[0]) | aten.cat.default (in[1]) | aten.mul.Tensor (in[1]) | aten.neg.default (in[0]) | aten.cat.default (in[1]) | aten.copy_.default (in[1]) | aten.copy_.default (in[1]) | aten.copy_.default (in[1]) | aten.mul.Tensor (in[0]) | aten.add.Tensor (in[1]) | aten.bmm.default (in[1]) | aten.transpose.int (in[0])</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 64], [1, 128, 64], [1, 128, 128, 192], [128, 128, 128], [128, 128, 128]</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32, torch.float32, torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>aten.index.Tensor (out[0]) | aten.index.Tensor (out[0]) | aten.new_empty.default (out[0]) | aten.bmm.default (out[0]) | aten.bmm.default (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.o_proj</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>[128, 16384], [16384, 7168]</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (in[0]) | aten.mm.default (in[1])</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>[128, 7168]</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>model.layers.0</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>aten.add.Tensor</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168], [1, 128, 7168]</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>aten.add.Tensor (in[0]) | aten.add.Tensor (in[1])</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168]</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>aten.add.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>post_attention_layernorm (DeepseekV3RMSNorm)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar → aten.mean.dim → aten.add.Tensor → aten.rsqrt.default → aten.mul.Tensor</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168], [7168]</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar (in[0]) | aten.mul.Tensor (in[0])</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168]</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>mlp (DeepseekV3MLP)</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default → aten.silu.default → aten.mul.Tensor</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>[7168, 18432], [1, 128, 18432]</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (in[1]) | aten.mul.Tensor (in[1])</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>[128, 18432], [128, 7168]</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (out[0]) | aten.mm.default (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>model.layers.0</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>aten.add.Tensor</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168], [1, 128, 7168]</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>aten.add.Tensor (in[0]) | aten.add.Tensor (in[1])</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168]</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>aten.add.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>input_layernorm (DeepseekV3RMSNorm)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar → aten.mean.dim → aten.add.Tensor → aten.rsqrt.default → aten.mul.Tensor</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168], [7168]</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar (in[0]) | aten.mul.Tensor (in[0])</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168]</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.q_a_proj</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>[128, 7168], [7168, 1536]</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (in[0]) | aten.mm.default (in[1])</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>[128, 1536]</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.q_a_layernorm (DeepseekV3RMSNorm)</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar → aten.mean.dim → aten.add.Tensor → aten.rsqrt.default → aten.mul.Tensor</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 1536], [1536]</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar (in[0]) | aten.mul.Tensor (in[0])</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 1536]</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.q_b_proj</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>[128, 1536], [1536, 24576]</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (in[0]) | aten.mm.default (in[1])</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>[128, 24576]</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>self_attn</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 128, 192]</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int (in[0])</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 128, 192]</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.kv_a_proj_with_mqa</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>[128, 7168], [7168, 576]</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (in[0]) | aten.mm.default (in[1])</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>[128, 576]</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>self_attn</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 1, 64]</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int (in[0])</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>[1, 1, 128, 64]</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.kv_a_layernorm (DeepseekV3RMSNorm)</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar → aten.mean.dim → aten.add.Tensor → aten.rsqrt.default → aten.mul.Tensor</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 512], [512]</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar (in[0]) | aten.mul.Tensor (in[0])</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 512]</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.kv_b_proj</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>[128, 512], [512, 32768]</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (in[0]) | aten.mm.default (in[1])</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>[128, 32768]</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>self_attn</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 128, 256]</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int (in[0])</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 128, 256]</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.rotary_emb (DeepseekV3YarnRotaryEmbedding)</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>aten.arange.start_step → aten.div.Tensor → aten.pow.Scalar → aten.reciprocal.default → aten.mul.Tensor → aten.sub.Tensor → aten.clamp.default → aten._to_copy.default → aten.rsub.Scalar → aten.add.Tensor → aten.cat.default → aten.cos.default → aten.sin.default</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>[128, 1]</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor (in[0])</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>[128, 64], [128, 64]</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor (out[0]) | aten.mul.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>self_attn (DeepseekV3Attention)</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>aten.index.Tensor → aten.transpose.int → aten.mul.Tensor → aten.neg.default → aten.cat.default → aten.add.Tensor → aten.new_empty.default → aten.copy_.default → aten.bmm.default → aten._softmax.default</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>[128, 64], [1, 128], [128, 64], [1, 128, 128, 64], [1, 1, 128, 64], [1, 128, 128, 32], [1, 128, 128, 32], [1, 1, 128, 64], [1, 1, 128, 32], [1, 1, 128, 32], [1, 128, 128, 128], [1, 128, 128, 128], [1, 128, 128, 64], [1, 128, 128, 128], [1, 1, 128, 128], [128, 128, 128], [1, 128, 128, 128]</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.int64, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>aten.index.Tensor (in[0]) | aten.index.Tensor (in[1]) | aten.index.Tensor (in[0]) | aten.mul.Tensor (in[0]) | aten.mul.Tensor (in[1]) | aten.neg.default (in[0]) | aten.cat.default (in[1]) | aten.mul.Tensor (in[1]) | aten.neg.default (in[0]) | aten.cat.default (in[1]) | aten.copy_.default (in[1]) | aten.copy_.default (in[1]) | aten.copy_.default (in[1]) | aten.mul.Tensor (in[0]) | aten.add.Tensor (in[1]) | aten.bmm.default (in[1]) | aten.transpose.int (in[0])</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 64], [1, 128, 64], [1, 128, 128, 192], [128, 128, 128], [128, 128, 128]</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32, torch.float32, torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>aten.index.Tensor (out[0]) | aten.index.Tensor (out[0]) | aten.new_empty.default (out[0]) | aten.bmm.default (out[0]) | aten.bmm.default (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.o_proj</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>[128, 16384], [16384, 7168]</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (in[0]) | aten.mm.default (in[1])</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>[128, 7168]</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>model.layers.1</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>aten.add.Tensor</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168], [1, 128, 7168]</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>aten.add.Tensor (in[0]) | aten.add.Tensor (in[1])</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168]</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>aten.add.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>post_attention_layernorm (DeepseekV3RMSNorm)</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar → aten.mean.dim → aten.add.Tensor → aten.rsqrt.default → aten.mul.Tensor</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168], [7168]</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar (in[0]) | aten.mul.Tensor (in[0])</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168]</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>mlp (DeepseekV3MLP)</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default → aten.silu.default → aten.mul.Tensor</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 18432]</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor (in[1])</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>[128, 7168]</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>model.layers.1</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>aten.add.Tensor</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168], [1, 128, 7168]</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>aten.add.Tensor (in[0]) | aten.add.Tensor (in[1])</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168]</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>aten.add.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>input_layernorm (DeepseekV3RMSNorm)</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar → aten.mean.dim → aten.add.Tensor → aten.rsqrt.default → aten.mul.Tensor</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168], [7168]</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar (in[0]) | aten.mul.Tensor (in[0])</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168]</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.q_a_proj</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>[128, 7168], [7168, 1536]</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (in[0]) | aten.mm.default (in[1])</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>[128, 1536]</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.q_a_layernorm (DeepseekV3RMSNorm)</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar → aten.mean.dim → aten.add.Tensor → aten.rsqrt.default → aten.mul.Tensor</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 1536], [1536]</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar (in[0]) | aten.mul.Tensor (in[0])</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 1536]</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.q_b_proj</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>[128, 1536], [1536, 24576]</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (in[0]) | aten.mm.default (in[1])</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>[128, 24576]</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>self_attn</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 128, 192]</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int (in[0])</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 128, 192]</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.kv_a_proj_with_mqa</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>[128, 7168], [7168, 576]</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (in[0]) | aten.mm.default (in[1])</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>[128, 576]</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>self_attn</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 1, 64]</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int (in[0])</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>[1, 1, 128, 64]</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.kv_a_layernorm (DeepseekV3RMSNorm)</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar → aten.mean.dim → aten.add.Tensor → aten.rsqrt.default → aten.mul.Tensor</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 512], [512]</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar (in[0]) | aten.mul.Tensor (in[0])</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 512]</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.kv_b_proj</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>[128, 512], [512, 32768]</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (in[0]) | aten.mm.default (in[1])</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>[128, 32768]</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>self_attn</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 128, 256]</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int (in[0])</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 128, 256]</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.rotary_emb (DeepseekV3YarnRotaryEmbedding)</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>aten.arange.start_step → aten.div.Tensor → aten.pow.Scalar → aten.reciprocal.default → aten.mul.Tensor → aten.sub.Tensor → aten.clamp.default → aten._to_copy.default → aten.rsub.Scalar → aten.add.Tensor → aten.cat.default → aten.cos.default → aten.sin.default</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>[128, 1]</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor (in[0])</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>[128, 64], [128, 64]</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor (out[0]) | aten.mul.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>self_attn (DeepseekV3Attention)</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>aten.index.Tensor → aten.transpose.int → aten.mul.Tensor → aten.neg.default → aten.cat.default → aten.add.Tensor → aten.new_empty.default → aten.copy_.default → aten.bmm.default → aten._softmax.default</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>[128, 64], [1, 128], [128, 64], [1, 128, 128, 64], [1, 1, 128, 64], [1, 128, 128, 32], [1, 128, 128, 32], [1, 1, 128, 64], [1, 1, 128, 32], [1, 1, 128, 32], [1, 128, 128, 128], [1, 128, 128, 128], [1, 128, 128, 64], [1, 128, 128, 128], [1, 1, 128, 128], [128, 128, 128], [1, 128, 128, 128]</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.int64, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>aten.index.Tensor (in[0]) | aten.index.Tensor (in[1]) | aten.index.Tensor (in[0]) | aten.mul.Tensor (in[0]) | aten.mul.Tensor (in[1]) | aten.neg.default (in[0]) | aten.cat.default (in[1]) | aten.mul.Tensor (in[1]) | aten.neg.default (in[0]) | aten.cat.default (in[1]) | aten.copy_.default (in[1]) | aten.copy_.default (in[1]) | aten.copy_.default (in[1]) | aten.mul.Tensor (in[0]) | aten.add.Tensor (in[1]) | aten.bmm.default (in[1]) | aten.transpose.int (in[0])</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 64], [1, 128, 64], [1, 128, 128, 192], [128, 128, 128], [128, 128, 128]</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32, torch.float32, torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>aten.index.Tensor (out[0]) | aten.index.Tensor (out[0]) | aten.new_empty.default (out[0]) | aten.bmm.default (out[0]) | aten.bmm.default (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.o_proj</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>[128, 16384], [16384, 7168]</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (in[0]) | aten.mm.default (in[1])</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>[128, 7168]</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>model.layers.2</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>aten.add.Tensor</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168], [1, 128, 7168]</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>aten.add.Tensor (in[0]) | aten.add.Tensor (in[1])</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168]</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>aten.add.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>post_attention_layernorm (DeepseekV3RMSNorm)</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar → aten.mean.dim → aten.add.Tensor → aten.rsqrt.default → aten.mul.Tensor</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168], [7168]</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar (in[0]) | aten.mul.Tensor (in[0])</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168]</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>mlp (DeepseekV3MLP)</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default → aten.silu.default → aten.mul.Tensor</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>[7168, 18432], [1, 128, 18432]</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (in[1]) | aten.mul.Tensor (in[1])</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>[128, 18432], [128, 7168]</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (out[0]) | aten.mm.default (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>model.layers.2</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>aten.add.Tensor</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168], [1, 128, 7168]</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>aten.add.Tensor (in[0]) | aten.add.Tensor (in[1])</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168]</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>aten.add.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>input_layernorm (DeepseekV3RMSNorm)</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar → aten.mean.dim → aten.add.Tensor → aten.rsqrt.default → aten.mul.Tensor</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168], [7168]</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar (in[0]) | aten.mul.Tensor (in[0])</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168]</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.q_a_proj</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>[128, 7168], [7168, 1536]</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (in[0]) | aten.mm.default (in[1])</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>[128, 1536]</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.q_a_layernorm (DeepseekV3RMSNorm)</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar → aten.mean.dim → aten.add.Tensor → aten.rsqrt.default → aten.mul.Tensor</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 1536], [1536]</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar (in[0]) | aten.mul.Tensor (in[0])</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 1536]</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.q_b_proj</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>[128, 1536], [1536, 24576]</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (in[0]) | aten.mm.default (in[1])</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>[128, 24576]</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>self_attn</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 128, 192]</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int (in[0])</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 128, 192]</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.kv_a_proj_with_mqa</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>[128, 7168], [7168, 576]</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (in[0]) | aten.mm.default (in[1])</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>[128, 576]</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>self_attn</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 1, 64]</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int (in[0])</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>[1, 1, 128, 64]</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.kv_a_layernorm (DeepseekV3RMSNorm)</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar → aten.mean.dim → aten.add.Tensor → aten.rsqrt.default → aten.mul.Tensor</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 512], [512]</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar (in[0]) | aten.mul.Tensor (in[0])</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 512]</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.kv_b_proj</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>[128, 512], [512, 32768]</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (in[0]) | aten.mm.default (in[1])</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>[128, 32768]</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>self_attn</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 128, 256]</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int (in[0])</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 128, 256]</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>aten.transpose.int (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.rotary_emb (DeepseekV3YarnRotaryEmbedding)</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>aten.arange.start_step → aten.div.Tensor → aten.pow.Scalar → aten.reciprocal.default → aten.mul.Tensor → aten.sub.Tensor → aten.clamp.default → aten._to_copy.default → aten.rsub.Scalar → aten.add.Tensor → aten.cat.default → aten.cos.default → aten.sin.default</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>[128, 1]</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor (in[0])</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>[128, 64], [128, 64]</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor (out[0]) | aten.mul.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>self_attn (DeepseekV3Attention)</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>aten.index.Tensor → aten.transpose.int → aten.mul.Tensor → aten.neg.default → aten.cat.default → aten.add.Tensor → aten.new_empty.default → aten.copy_.default → aten.bmm.default → aten._softmax.default</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>[128, 64], [1, 128], [128, 64], [1, 128, 128, 64], [1, 1, 128, 64], [1, 128, 128, 32], [1, 128, 128, 32], [1, 1, 128, 64], [1, 1, 128, 32], [1, 1, 128, 32], [1, 128, 128, 128], [1, 128, 128, 128], [1, 128, 128, 64], [1, 128, 128, 128], [1, 1, 128, 128], [128, 128, 128], [1, 128, 128, 128]</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.int64, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>aten.index.Tensor (in[0]) | aten.index.Tensor (in[1]) | aten.index.Tensor (in[0]) | aten.mul.Tensor (in[0]) | aten.mul.Tensor (in[1]) | aten.neg.default (in[0]) | aten.cat.default (in[1]) | aten.mul.Tensor (in[1]) | aten.neg.default (in[0]) | aten.cat.default (in[1]) | aten.copy_.default (in[1]) | aten.copy_.default (in[1]) | aten.copy_.default (in[1]) | aten.mul.Tensor (in[0]) | aten.add.Tensor (in[1]) | aten.bmm.default (in[1]) | aten.transpose.int (in[0])</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 64], [1, 128, 64], [1, 128, 128, 192], [128, 128, 128], [128, 128, 128]</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32, torch.float32, torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>aten.index.Tensor (out[0]) | aten.index.Tensor (out[0]) | aten.new_empty.default (out[0]) | aten.bmm.default (out[0]) | aten.bmm.default (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>self_attn.o_proj</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>[128, 16384], [16384, 7168]</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (in[0]) | aten.mm.default (in[1])</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>[128, 7168]</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>model.layers.3</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>aten.add.Tensor</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168], [1, 128, 7168]</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>aten.add.Tensor (in[0]) | aten.add.Tensor (in[1])</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168]</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>aten.add.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>post_attention_layernorm (DeepseekV3RMSNorm)</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar → aten.mean.dim → aten.add.Tensor → aten.rsqrt.default → aten.mul.Tensor</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168], [7168]</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar (in[0]) | aten.mul.Tensor (in[0])</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168]</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>mlp.gate (MoEGate)</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default → aten.sigmoid.default → aten.add.Tensor → aten.topk.default → aten.sum.dim_IntList → aten._to_copy.default → aten.masked_fill.Scalar → aten.gather.default → aten.div.Tensor → aten.mul.Tensor</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>[128, 7168]</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (in[0])</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>[128, 4], [128, 256], [128, 8]</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>torch.int64, torch.bool, torch.float32</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>aten.topk.default (out[1]) | aten._to_copy.default (out[0]) | aten.mul.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>mlp.experts.0 (DeepseekV3MLP)</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default → aten.silu.default → aten.mul.Tensor</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>[128, 7168]</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (in[0])</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr"/>
+      <c r="J70" s="4" t="inlineStr"/>
+      <c r="K70" s="4" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>mlp</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>[128, 7168], [128, 1]</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor (in[0]) | aten.mul.Tensor (in[1])</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>[128, 7168]</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>mlp.shared_experts (DeepseekV3MLP)</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default → aten.silu.default → aten.mul.Tensor</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>[7168, 2048], [1, 128, 2048]</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (in[1]) | aten.mul.Tensor (in[1])</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>[128, 2048], [128, 7168]</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (out[0]) | aten.mm.default (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>mlp</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>aten.add.Tensor</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168], [1, 128, 7168]</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>aten.add.Tensor (in[0]) | aten.add.Tensor (in[1])</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168]</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>aten.add.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>model.layers.3</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>aten.add.Tensor</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168], [1, 128, 7168]</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>aten.add.Tensor (in[0]) | aten.add.Tensor (in[1])</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168]</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>aten.add.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>model.norm (DeepseekV3RMSNorm)</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar → aten.mean.dim → aten.add.Tensor → aten.rsqrt.default → aten.mul.Tensor</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168], [7168]</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar (in[0]) | aten.mul.Tensor (in[0])</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168]</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>lm_head</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>aten.mm.default</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" s="6" t="inlineStr"/>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>[128, 7168], [7168, 129280]</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>aten.mm.default (in[0]) | aten.mm.default (in[1])</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>[128, 129280]</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="K76" s="6" t="inlineStr">
+        <is>
+          <t>aten.mm.default (out[0])</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K76"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -848,164 +4897,164 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>aten.embedding.default</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>model.embed_tokens</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr"/>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr"/>
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>embedding</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>[129280, 7168], [1, 128]</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>torch.float32, torch.int64</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>[1, 128, 7168]</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>aten.rsub.Scalar</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr"/>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>rsub</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>[1, 1, 128, 128]</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>torch.float32</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>[1, 1, 128, 128]</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>aten._to_copy.default</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr"/>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>_to_copy</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>[1, 1, 128, 128]</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>torch.float32</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>[1, 1, 128, 128]</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>torch.bool</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>aten.masked_fill.Scalar</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>masked_fill</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>[1, 1, 128, 128], [1, 1, 128, 128]</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>torch.float32, torch.bool</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>[1, 1, 128, 128]</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
@@ -4551,45 +8600,45 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="n">
+      <c r="A85" s="11" t="n">
         <v>83</v>
       </c>
-      <c r="B85" s="6" t="inlineStr">
+      <c r="B85" s="12" t="inlineStr">
         <is>
           <t>aten.add.Tensor</t>
         </is>
       </c>
-      <c r="C85" s="6" t="inlineStr">
+      <c r="C85" s="12" t="inlineStr">
         <is>
           <t>model.layers.0</t>
         </is>
       </c>
-      <c r="D85" s="6" t="inlineStr">
+      <c r="D85" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="E85" s="12" t="inlineStr">
         <is>
           <t>add</t>
         </is>
       </c>
-      <c r="F85" s="6" t="inlineStr">
+      <c r="F85" s="12" t="inlineStr">
         <is>
           <t>[1, 128, 7168], [1, 128, 7168]</t>
         </is>
       </c>
-      <c r="G85" s="6" t="inlineStr">
+      <c r="G85" s="12" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H85" s="6" t="inlineStr">
+      <c r="H85" s="12" t="inlineStr">
         <is>
           <t>[1, 128, 7168]</t>
         </is>
       </c>
-      <c r="I85" s="6" t="inlineStr">
+      <c r="I85" s="12" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
@@ -4866,270 +8915,270 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="11" t="n">
+      <c r="A92" s="13" t="n">
         <v>90</v>
       </c>
-      <c r="B92" s="12" t="inlineStr">
+      <c r="B92" s="14" t="inlineStr">
         <is>
           <t>aten.mm.default</t>
         </is>
       </c>
-      <c r="C92" s="12" t="inlineStr">
+      <c r="C92" s="14" t="inlineStr">
         <is>
           <t>model.layers.0.mlp.gate_proj</t>
         </is>
       </c>
-      <c r="D92" s="12" t="inlineStr">
+      <c r="D92" s="14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E92" s="12" t="inlineStr">
+      <c r="E92" s="14" t="inlineStr">
         <is>
           <t>moe.gate.mm</t>
         </is>
       </c>
-      <c r="F92" s="12" t="inlineStr">
+      <c r="F92" s="14" t="inlineStr">
         <is>
           <t>[128, 7168], [7168, 18432]</t>
         </is>
       </c>
-      <c r="G92" s="12" t="inlineStr">
+      <c r="G92" s="14" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H92" s="12" t="inlineStr">
+      <c r="H92" s="14" t="inlineStr">
         <is>
           <t>[128, 18432]</t>
         </is>
       </c>
-      <c r="I92" s="12" t="inlineStr">
+      <c r="I92" s="14" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="13" t="n">
+      <c r="A93" s="15" t="n">
         <v>91</v>
       </c>
-      <c r="B93" s="14" t="inlineStr">
+      <c r="B93" s="16" t="inlineStr">
         <is>
           <t>aten.silu.default</t>
         </is>
       </c>
-      <c r="C93" s="14" t="inlineStr">
+      <c r="C93" s="16" t="inlineStr">
         <is>
           <t>model.layers.0.mlp.act_fn</t>
         </is>
       </c>
-      <c r="D93" s="14" t="inlineStr">
+      <c r="D93" s="16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E93" s="14" t="inlineStr">
+      <c r="E93" s="16" t="inlineStr">
         <is>
           <t>ffn.silu</t>
         </is>
       </c>
-      <c r="F93" s="14" t="inlineStr">
+      <c r="F93" s="16" t="inlineStr">
         <is>
           <t>[1, 128, 18432]</t>
         </is>
       </c>
-      <c r="G93" s="14" t="inlineStr">
-        <is>
-          <t>torch.float32</t>
-        </is>
-      </c>
-      <c r="H93" s="14" t="inlineStr">
+      <c r="G93" s="16" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H93" s="16" t="inlineStr">
         <is>
           <t>[1, 128, 18432]</t>
         </is>
       </c>
-      <c r="I93" s="14" t="inlineStr">
+      <c r="I93" s="16" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="13" t="n">
+      <c r="A94" s="15" t="n">
         <v>92</v>
       </c>
-      <c r="B94" s="14" t="inlineStr">
+      <c r="B94" s="16" t="inlineStr">
         <is>
           <t>aten.mm.default</t>
         </is>
       </c>
-      <c r="C94" s="14" t="inlineStr">
+      <c r="C94" s="16" t="inlineStr">
         <is>
           <t>model.layers.0.mlp.up_proj</t>
         </is>
       </c>
-      <c r="D94" s="14" t="inlineStr">
+      <c r="D94" s="16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E94" s="14" t="inlineStr">
+      <c r="E94" s="16" t="inlineStr">
         <is>
           <t>ffn.up_proj</t>
         </is>
       </c>
-      <c r="F94" s="14" t="inlineStr">
+      <c r="F94" s="16" t="inlineStr">
         <is>
           <t>[128, 7168], [7168, 18432]</t>
         </is>
       </c>
-      <c r="G94" s="14" t="inlineStr">
+      <c r="G94" s="16" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H94" s="14" t="inlineStr">
+      <c r="H94" s="16" t="inlineStr">
         <is>
           <t>[128, 18432]</t>
         </is>
       </c>
-      <c r="I94" s="14" t="inlineStr">
+      <c r="I94" s="16" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="13" t="n">
+      <c r="A95" s="15" t="n">
         <v>93</v>
       </c>
-      <c r="B95" s="14" t="inlineStr">
+      <c r="B95" s="16" t="inlineStr">
         <is>
           <t>aten.mul.Tensor</t>
         </is>
       </c>
-      <c r="C95" s="14" t="inlineStr">
+      <c r="C95" s="16" t="inlineStr">
         <is>
           <t>model.layers.0.mlp</t>
         </is>
       </c>
-      <c r="D95" s="14" t="inlineStr">
+      <c r="D95" s="16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E95" s="14" t="inlineStr">
+      <c r="E95" s="16" t="inlineStr">
         <is>
           <t>ffn.mul</t>
         </is>
       </c>
-      <c r="F95" s="14" t="inlineStr">
+      <c r="F95" s="16" t="inlineStr">
         <is>
           <t>[1, 128, 18432], [1, 128, 18432]</t>
         </is>
       </c>
-      <c r="G95" s="14" t="inlineStr">
+      <c r="G95" s="16" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H95" s="14" t="inlineStr">
+      <c r="H95" s="16" t="inlineStr">
         <is>
           <t>[1, 128, 18432]</t>
         </is>
       </c>
-      <c r="I95" s="14" t="inlineStr">
+      <c r="I95" s="16" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="13" t="n">
+      <c r="A96" s="15" t="n">
         <v>94</v>
       </c>
-      <c r="B96" s="14" t="inlineStr">
+      <c r="B96" s="16" t="inlineStr">
         <is>
           <t>aten.mm.default</t>
         </is>
       </c>
-      <c r="C96" s="14" t="inlineStr">
+      <c r="C96" s="16" t="inlineStr">
         <is>
           <t>model.layers.0.mlp.down_proj</t>
         </is>
       </c>
-      <c r="D96" s="14" t="inlineStr">
+      <c r="D96" s="16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E96" s="14" t="inlineStr">
+      <c r="E96" s="16" t="inlineStr">
         <is>
           <t>ffn.down_proj</t>
         </is>
       </c>
-      <c r="F96" s="14" t="inlineStr">
+      <c r="F96" s="16" t="inlineStr">
         <is>
           <t>[128, 18432], [18432, 7168]</t>
         </is>
       </c>
-      <c r="G96" s="14" t="inlineStr">
+      <c r="G96" s="16" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H96" s="14" t="inlineStr">
+      <c r="H96" s="16" t="inlineStr">
         <is>
           <t>[128, 7168]</t>
         </is>
       </c>
-      <c r="I96" s="14" t="inlineStr">
+      <c r="I96" s="16" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="n">
+      <c r="A97" s="11" t="n">
         <v>95</v>
       </c>
-      <c r="B97" s="6" t="inlineStr">
+      <c r="B97" s="12" t="inlineStr">
         <is>
           <t>aten.add.Tensor</t>
         </is>
       </c>
-      <c r="C97" s="6" t="inlineStr">
+      <c r="C97" s="12" t="inlineStr">
         <is>
           <t>model.layers.0</t>
         </is>
       </c>
-      <c r="D97" s="6" t="inlineStr">
+      <c r="D97" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E97" s="6" t="inlineStr">
+      <c r="E97" s="12" t="inlineStr">
         <is>
           <t>add</t>
         </is>
       </c>
-      <c r="F97" s="6" t="inlineStr">
+      <c r="F97" s="12" t="inlineStr">
         <is>
           <t>[1, 128, 7168], [1, 128, 7168]</t>
         </is>
       </c>
-      <c r="G97" s="6" t="inlineStr">
+      <c r="G97" s="12" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H97" s="6" t="inlineStr">
+      <c r="H97" s="12" t="inlineStr">
         <is>
           <t>[1, 128, 7168]</t>
         </is>
       </c>
-      <c r="I97" s="6" t="inlineStr">
+      <c r="I97" s="12" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
@@ -8675,45 +12724,45 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="5" t="n">
+      <c r="A177" s="11" t="n">
         <v>175</v>
       </c>
-      <c r="B177" s="6" t="inlineStr">
+      <c r="B177" s="12" t="inlineStr">
         <is>
           <t>aten.add.Tensor</t>
         </is>
       </c>
-      <c r="C177" s="6" t="inlineStr">
+      <c r="C177" s="12" t="inlineStr">
         <is>
           <t>model.layers.1</t>
         </is>
       </c>
-      <c r="D177" s="6" t="inlineStr">
+      <c r="D177" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E177" s="6" t="inlineStr">
+      <c r="E177" s="12" t="inlineStr">
         <is>
           <t>add</t>
         </is>
       </c>
-      <c r="F177" s="6" t="inlineStr">
+      <c r="F177" s="12" t="inlineStr">
         <is>
           <t>[1, 128, 7168], [1, 128, 7168]</t>
         </is>
       </c>
-      <c r="G177" s="6" t="inlineStr">
+      <c r="G177" s="12" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H177" s="6" t="inlineStr">
+      <c r="H177" s="12" t="inlineStr">
         <is>
           <t>[1, 128, 7168]</t>
         </is>
       </c>
-      <c r="I177" s="6" t="inlineStr">
+      <c r="I177" s="12" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
@@ -8990,270 +13039,270 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="11" t="n">
+      <c r="A184" s="13" t="n">
         <v>182</v>
       </c>
-      <c r="B184" s="12" t="inlineStr">
+      <c r="B184" s="14" t="inlineStr">
         <is>
           <t>aten.mm.default</t>
         </is>
       </c>
-      <c r="C184" s="12" t="inlineStr">
+      <c r="C184" s="14" t="inlineStr">
         <is>
           <t>model.layers.1.mlp.gate_proj</t>
         </is>
       </c>
-      <c r="D184" s="12" t="inlineStr">
+      <c r="D184" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E184" s="12" t="inlineStr">
+      <c r="E184" s="14" t="inlineStr">
         <is>
           <t>moe.gate.mm</t>
         </is>
       </c>
-      <c r="F184" s="12" t="inlineStr">
+      <c r="F184" s="14" t="inlineStr">
         <is>
           <t>[128, 7168], [7168, 18432]</t>
         </is>
       </c>
-      <c r="G184" s="12" t="inlineStr">
+      <c r="G184" s="14" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H184" s="12" t="inlineStr">
+      <c r="H184" s="14" t="inlineStr">
         <is>
           <t>[128, 18432]</t>
         </is>
       </c>
-      <c r="I184" s="12" t="inlineStr">
+      <c r="I184" s="14" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="13" t="n">
+      <c r="A185" s="15" t="n">
         <v>183</v>
       </c>
-      <c r="B185" s="14" t="inlineStr">
+      <c r="B185" s="16" t="inlineStr">
         <is>
           <t>aten.silu.default</t>
         </is>
       </c>
-      <c r="C185" s="14" t="inlineStr">
+      <c r="C185" s="16" t="inlineStr">
         <is>
           <t>model.layers.1.mlp.act_fn</t>
         </is>
       </c>
-      <c r="D185" s="14" t="inlineStr">
+      <c r="D185" s="16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E185" s="14" t="inlineStr">
+      <c r="E185" s="16" t="inlineStr">
         <is>
           <t>ffn.silu</t>
         </is>
       </c>
-      <c r="F185" s="14" t="inlineStr">
+      <c r="F185" s="16" t="inlineStr">
         <is>
           <t>[1, 128, 18432]</t>
         </is>
       </c>
-      <c r="G185" s="14" t="inlineStr">
-        <is>
-          <t>torch.float32</t>
-        </is>
-      </c>
-      <c r="H185" s="14" t="inlineStr">
+      <c r="G185" s="16" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H185" s="16" t="inlineStr">
         <is>
           <t>[1, 128, 18432]</t>
         </is>
       </c>
-      <c r="I185" s="14" t="inlineStr">
+      <c r="I185" s="16" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="13" t="n">
+      <c r="A186" s="15" t="n">
         <v>184</v>
       </c>
-      <c r="B186" s="14" t="inlineStr">
+      <c r="B186" s="16" t="inlineStr">
         <is>
           <t>aten.mm.default</t>
         </is>
       </c>
-      <c r="C186" s="14" t="inlineStr">
+      <c r="C186" s="16" t="inlineStr">
         <is>
           <t>model.layers.1.mlp.up_proj</t>
         </is>
       </c>
-      <c r="D186" s="14" t="inlineStr">
+      <c r="D186" s="16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E186" s="14" t="inlineStr">
+      <c r="E186" s="16" t="inlineStr">
         <is>
           <t>ffn.up_proj</t>
         </is>
       </c>
-      <c r="F186" s="14" t="inlineStr">
+      <c r="F186" s="16" t="inlineStr">
         <is>
           <t>[128, 7168], [7168, 18432]</t>
         </is>
       </c>
-      <c r="G186" s="14" t="inlineStr">
+      <c r="G186" s="16" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H186" s="14" t="inlineStr">
+      <c r="H186" s="16" t="inlineStr">
         <is>
           <t>[128, 18432]</t>
         </is>
       </c>
-      <c r="I186" s="14" t="inlineStr">
+      <c r="I186" s="16" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="13" t="n">
+      <c r="A187" s="15" t="n">
         <v>185</v>
       </c>
-      <c r="B187" s="14" t="inlineStr">
+      <c r="B187" s="16" t="inlineStr">
         <is>
           <t>aten.mul.Tensor</t>
         </is>
       </c>
-      <c r="C187" s="14" t="inlineStr">
+      <c r="C187" s="16" t="inlineStr">
         <is>
           <t>model.layers.1.mlp</t>
         </is>
       </c>
-      <c r="D187" s="14" t="inlineStr">
+      <c r="D187" s="16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E187" s="14" t="inlineStr">
+      <c r="E187" s="16" t="inlineStr">
         <is>
           <t>ffn.mul</t>
         </is>
       </c>
-      <c r="F187" s="14" t="inlineStr">
+      <c r="F187" s="16" t="inlineStr">
         <is>
           <t>[1, 128, 18432], [1, 128, 18432]</t>
         </is>
       </c>
-      <c r="G187" s="14" t="inlineStr">
+      <c r="G187" s="16" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H187" s="14" t="inlineStr">
+      <c r="H187" s="16" t="inlineStr">
         <is>
           <t>[1, 128, 18432]</t>
         </is>
       </c>
-      <c r="I187" s="14" t="inlineStr">
+      <c r="I187" s="16" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="13" t="n">
+      <c r="A188" s="15" t="n">
         <v>186</v>
       </c>
-      <c r="B188" s="14" t="inlineStr">
+      <c r="B188" s="16" t="inlineStr">
         <is>
           <t>aten.mm.default</t>
         </is>
       </c>
-      <c r="C188" s="14" t="inlineStr">
+      <c r="C188" s="16" t="inlineStr">
         <is>
           <t>model.layers.1.mlp.down_proj</t>
         </is>
       </c>
-      <c r="D188" s="14" t="inlineStr">
+      <c r="D188" s="16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E188" s="14" t="inlineStr">
+      <c r="E188" s="16" t="inlineStr">
         <is>
           <t>ffn.down_proj</t>
         </is>
       </c>
-      <c r="F188" s="14" t="inlineStr">
+      <c r="F188" s="16" t="inlineStr">
         <is>
           <t>[128, 18432], [18432, 7168]</t>
         </is>
       </c>
-      <c r="G188" s="14" t="inlineStr">
+      <c r="G188" s="16" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H188" s="14" t="inlineStr">
+      <c r="H188" s="16" t="inlineStr">
         <is>
           <t>[128, 7168]</t>
         </is>
       </c>
-      <c r="I188" s="14" t="inlineStr">
+      <c r="I188" s="16" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="5" t="n">
+      <c r="A189" s="11" t="n">
         <v>187</v>
       </c>
-      <c r="B189" s="6" t="inlineStr">
+      <c r="B189" s="12" t="inlineStr">
         <is>
           <t>aten.add.Tensor</t>
         </is>
       </c>
-      <c r="C189" s="6" t="inlineStr">
+      <c r="C189" s="12" t="inlineStr">
         <is>
           <t>model.layers.1</t>
         </is>
       </c>
-      <c r="D189" s="6" t="inlineStr">
+      <c r="D189" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E189" s="6" t="inlineStr">
+      <c r="E189" s="12" t="inlineStr">
         <is>
           <t>add</t>
         </is>
       </c>
-      <c r="F189" s="6" t="inlineStr">
+      <c r="F189" s="12" t="inlineStr">
         <is>
           <t>[1, 128, 7168], [1, 128, 7168]</t>
         </is>
       </c>
-      <c r="G189" s="6" t="inlineStr">
+      <c r="G189" s="12" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H189" s="6" t="inlineStr">
+      <c r="H189" s="12" t="inlineStr">
         <is>
           <t>[1, 128, 7168]</t>
         </is>
       </c>
-      <c r="I189" s="6" t="inlineStr">
+      <c r="I189" s="12" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
@@ -12799,45 +16848,45 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="5" t="n">
+      <c r="A269" s="11" t="n">
         <v>267</v>
       </c>
-      <c r="B269" s="6" t="inlineStr">
+      <c r="B269" s="12" t="inlineStr">
         <is>
           <t>aten.add.Tensor</t>
         </is>
       </c>
-      <c r="C269" s="6" t="inlineStr">
+      <c r="C269" s="12" t="inlineStr">
         <is>
           <t>model.layers.2</t>
         </is>
       </c>
-      <c r="D269" s="6" t="inlineStr">
+      <c r="D269" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E269" s="6" t="inlineStr">
+      <c r="E269" s="12" t="inlineStr">
         <is>
           <t>add</t>
         </is>
       </c>
-      <c r="F269" s="6" t="inlineStr">
+      <c r="F269" s="12" t="inlineStr">
         <is>
           <t>[1, 128, 7168], [1, 128, 7168]</t>
         </is>
       </c>
-      <c r="G269" s="6" t="inlineStr">
+      <c r="G269" s="12" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H269" s="6" t="inlineStr">
+      <c r="H269" s="12" t="inlineStr">
         <is>
           <t>[1, 128, 7168]</t>
         </is>
       </c>
-      <c r="I269" s="6" t="inlineStr">
+      <c r="I269" s="12" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
@@ -13114,270 +17163,270 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="11" t="n">
+      <c r="A276" s="13" t="n">
         <v>274</v>
       </c>
-      <c r="B276" s="12" t="inlineStr">
+      <c r="B276" s="14" t="inlineStr">
         <is>
           <t>aten.mm.default</t>
         </is>
       </c>
-      <c r="C276" s="12" t="inlineStr">
+      <c r="C276" s="14" t="inlineStr">
         <is>
           <t>model.layers.2.mlp.gate_proj</t>
         </is>
       </c>
-      <c r="D276" s="12" t="inlineStr">
+      <c r="D276" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E276" s="12" t="inlineStr">
+      <c r="E276" s="14" t="inlineStr">
         <is>
           <t>moe.gate.mm</t>
         </is>
       </c>
-      <c r="F276" s="12" t="inlineStr">
+      <c r="F276" s="14" t="inlineStr">
         <is>
           <t>[128, 7168], [7168, 18432]</t>
         </is>
       </c>
-      <c r="G276" s="12" t="inlineStr">
+      <c r="G276" s="14" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H276" s="12" t="inlineStr">
+      <c r="H276" s="14" t="inlineStr">
         <is>
           <t>[128, 18432]</t>
         </is>
       </c>
-      <c r="I276" s="12" t="inlineStr">
+      <c r="I276" s="14" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="13" t="n">
+      <c r="A277" s="15" t="n">
         <v>275</v>
       </c>
-      <c r="B277" s="14" t="inlineStr">
+      <c r="B277" s="16" t="inlineStr">
         <is>
           <t>aten.silu.default</t>
         </is>
       </c>
-      <c r="C277" s="14" t="inlineStr">
+      <c r="C277" s="16" t="inlineStr">
         <is>
           <t>model.layers.2.mlp.act_fn</t>
         </is>
       </c>
-      <c r="D277" s="14" t="inlineStr">
+      <c r="D277" s="16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E277" s="14" t="inlineStr">
+      <c r="E277" s="16" t="inlineStr">
         <is>
           <t>ffn.silu</t>
         </is>
       </c>
-      <c r="F277" s="14" t="inlineStr">
+      <c r="F277" s="16" t="inlineStr">
         <is>
           <t>[1, 128, 18432]</t>
         </is>
       </c>
-      <c r="G277" s="14" t="inlineStr">
-        <is>
-          <t>torch.float32</t>
-        </is>
-      </c>
-      <c r="H277" s="14" t="inlineStr">
+      <c r="G277" s="16" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H277" s="16" t="inlineStr">
         <is>
           <t>[1, 128, 18432]</t>
         </is>
       </c>
-      <c r="I277" s="14" t="inlineStr">
+      <c r="I277" s="16" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="13" t="n">
+      <c r="A278" s="15" t="n">
         <v>276</v>
       </c>
-      <c r="B278" s="14" t="inlineStr">
+      <c r="B278" s="16" t="inlineStr">
         <is>
           <t>aten.mm.default</t>
         </is>
       </c>
-      <c r="C278" s="14" t="inlineStr">
+      <c r="C278" s="16" t="inlineStr">
         <is>
           <t>model.layers.2.mlp.up_proj</t>
         </is>
       </c>
-      <c r="D278" s="14" t="inlineStr">
+      <c r="D278" s="16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E278" s="14" t="inlineStr">
+      <c r="E278" s="16" t="inlineStr">
         <is>
           <t>ffn.up_proj</t>
         </is>
       </c>
-      <c r="F278" s="14" t="inlineStr">
+      <c r="F278" s="16" t="inlineStr">
         <is>
           <t>[128, 7168], [7168, 18432]</t>
         </is>
       </c>
-      <c r="G278" s="14" t="inlineStr">
+      <c r="G278" s="16" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H278" s="14" t="inlineStr">
+      <c r="H278" s="16" t="inlineStr">
         <is>
           <t>[128, 18432]</t>
         </is>
       </c>
-      <c r="I278" s="14" t="inlineStr">
+      <c r="I278" s="16" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="13" t="n">
+      <c r="A279" s="15" t="n">
         <v>277</v>
       </c>
-      <c r="B279" s="14" t="inlineStr">
+      <c r="B279" s="16" t="inlineStr">
         <is>
           <t>aten.mul.Tensor</t>
         </is>
       </c>
-      <c r="C279" s="14" t="inlineStr">
+      <c r="C279" s="16" t="inlineStr">
         <is>
           <t>model.layers.2.mlp</t>
         </is>
       </c>
-      <c r="D279" s="14" t="inlineStr">
+      <c r="D279" s="16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E279" s="14" t="inlineStr">
+      <c r="E279" s="16" t="inlineStr">
         <is>
           <t>ffn.mul</t>
         </is>
       </c>
-      <c r="F279" s="14" t="inlineStr">
+      <c r="F279" s="16" t="inlineStr">
         <is>
           <t>[1, 128, 18432], [1, 128, 18432]</t>
         </is>
       </c>
-      <c r="G279" s="14" t="inlineStr">
+      <c r="G279" s="16" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H279" s="14" t="inlineStr">
+      <c r="H279" s="16" t="inlineStr">
         <is>
           <t>[1, 128, 18432]</t>
         </is>
       </c>
-      <c r="I279" s="14" t="inlineStr">
+      <c r="I279" s="16" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="13" t="n">
+      <c r="A280" s="15" t="n">
         <v>278</v>
       </c>
-      <c r="B280" s="14" t="inlineStr">
+      <c r="B280" s="16" t="inlineStr">
         <is>
           <t>aten.mm.default</t>
         </is>
       </c>
-      <c r="C280" s="14" t="inlineStr">
+      <c r="C280" s="16" t="inlineStr">
         <is>
           <t>model.layers.2.mlp.down_proj</t>
         </is>
       </c>
-      <c r="D280" s="14" t="inlineStr">
+      <c r="D280" s="16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E280" s="14" t="inlineStr">
+      <c r="E280" s="16" t="inlineStr">
         <is>
           <t>ffn.down_proj</t>
         </is>
       </c>
-      <c r="F280" s="14" t="inlineStr">
+      <c r="F280" s="16" t="inlineStr">
         <is>
           <t>[128, 18432], [18432, 7168]</t>
         </is>
       </c>
-      <c r="G280" s="14" t="inlineStr">
+      <c r="G280" s="16" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H280" s="14" t="inlineStr">
+      <c r="H280" s="16" t="inlineStr">
         <is>
           <t>[128, 7168]</t>
         </is>
       </c>
-      <c r="I280" s="14" t="inlineStr">
+      <c r="I280" s="16" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="5" t="n">
+      <c r="A281" s="11" t="n">
         <v>279</v>
       </c>
-      <c r="B281" s="6" t="inlineStr">
+      <c r="B281" s="12" t="inlineStr">
         <is>
           <t>aten.add.Tensor</t>
         </is>
       </c>
-      <c r="C281" s="6" t="inlineStr">
+      <c r="C281" s="12" t="inlineStr">
         <is>
           <t>model.layers.2</t>
         </is>
       </c>
-      <c r="D281" s="6" t="inlineStr">
+      <c r="D281" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E281" s="6" t="inlineStr">
+      <c r="E281" s="12" t="inlineStr">
         <is>
           <t>add</t>
         </is>
       </c>
-      <c r="F281" s="6" t="inlineStr">
+      <c r="F281" s="12" t="inlineStr">
         <is>
           <t>[1, 128, 7168], [1, 128, 7168]</t>
         </is>
       </c>
-      <c r="G281" s="6" t="inlineStr">
+      <c r="G281" s="12" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H281" s="6" t="inlineStr">
+      <c r="H281" s="12" t="inlineStr">
         <is>
           <t>[1, 128, 7168]</t>
         </is>
       </c>
-      <c r="I281" s="6" t="inlineStr">
+      <c r="I281" s="12" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
@@ -16923,45 +20972,45 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="5" t="n">
+      <c r="A361" s="11" t="n">
         <v>359</v>
       </c>
-      <c r="B361" s="6" t="inlineStr">
+      <c r="B361" s="12" t="inlineStr">
         <is>
           <t>aten.add.Tensor</t>
         </is>
       </c>
-      <c r="C361" s="6" t="inlineStr">
+      <c r="C361" s="12" t="inlineStr">
         <is>
           <t>model.layers.3</t>
         </is>
       </c>
-      <c r="D361" s="6" t="inlineStr">
+      <c r="D361" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E361" s="6" t="inlineStr">
+      <c r="E361" s="12" t="inlineStr">
         <is>
           <t>add</t>
         </is>
       </c>
-      <c r="F361" s="6" t="inlineStr">
+      <c r="F361" s="12" t="inlineStr">
         <is>
           <t>[1, 128, 7168], [1, 128, 7168]</t>
         </is>
       </c>
-      <c r="G361" s="6" t="inlineStr">
+      <c r="G361" s="12" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H361" s="6" t="inlineStr">
+      <c r="H361" s="12" t="inlineStr">
         <is>
           <t>[1, 128, 7168]</t>
         </is>
       </c>
-      <c r="I361" s="6" t="inlineStr">
+      <c r="I361" s="12" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
@@ -17238,1215 +21287,1215 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="11" t="n">
+      <c r="A368" s="13" t="n">
         <v>366</v>
       </c>
-      <c r="B368" s="12" t="inlineStr">
+      <c r="B368" s="14" t="inlineStr">
         <is>
           <t>aten.mm.default</t>
         </is>
       </c>
-      <c r="C368" s="12" t="inlineStr">
+      <c r="C368" s="14" t="inlineStr">
         <is>
           <t>model.layers.3.mlp.gate</t>
         </is>
       </c>
-      <c r="D368" s="12" t="inlineStr">
+      <c r="D368" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E368" s="12" t="inlineStr">
+      <c r="E368" s="14" t="inlineStr">
         <is>
           <t>moe.gate.mm</t>
         </is>
       </c>
-      <c r="F368" s="12" t="inlineStr">
+      <c r="F368" s="14" t="inlineStr">
         <is>
           <t>[128, 7168], [7168, 256]</t>
         </is>
       </c>
-      <c r="G368" s="12" t="inlineStr">
+      <c r="G368" s="14" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H368" s="12" t="inlineStr">
+      <c r="H368" s="14" t="inlineStr">
         <is>
           <t>[128, 256]</t>
         </is>
       </c>
-      <c r="I368" s="12" t="inlineStr">
+      <c r="I368" s="14" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="11" t="n">
+      <c r="A369" s="13" t="n">
         <v>367</v>
       </c>
-      <c r="B369" s="12" t="inlineStr">
+      <c r="B369" s="14" t="inlineStr">
         <is>
           <t>aten.sigmoid.default</t>
         </is>
       </c>
-      <c r="C369" s="12" t="inlineStr">
+      <c r="C369" s="14" t="inlineStr">
         <is>
           <t>model.layers.3.mlp.gate</t>
         </is>
       </c>
-      <c r="D369" s="12" t="inlineStr">
+      <c r="D369" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E369" s="12" t="inlineStr">
+      <c r="E369" s="14" t="inlineStr">
         <is>
           <t>moe.gate.sigmoid</t>
         </is>
       </c>
-      <c r="F369" s="12" t="inlineStr">
+      <c r="F369" s="14" t="inlineStr">
         <is>
           <t>[128, 256]</t>
         </is>
       </c>
-      <c r="G369" s="12" t="inlineStr">
-        <is>
-          <t>torch.float32</t>
-        </is>
-      </c>
-      <c r="H369" s="12" t="inlineStr">
+      <c r="G369" s="14" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H369" s="14" t="inlineStr">
         <is>
           <t>[128, 256]</t>
         </is>
       </c>
-      <c r="I369" s="12" t="inlineStr">
+      <c r="I369" s="14" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="11" t="n">
+      <c r="A370" s="13" t="n">
         <v>368</v>
       </c>
-      <c r="B370" s="12" t="inlineStr">
+      <c r="B370" s="14" t="inlineStr">
         <is>
           <t>aten.add.Tensor</t>
         </is>
       </c>
-      <c r="C370" s="12" t="inlineStr">
+      <c r="C370" s="14" t="inlineStr">
         <is>
           <t>model.layers.3.mlp.gate</t>
         </is>
       </c>
-      <c r="D370" s="12" t="inlineStr">
+      <c r="D370" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E370" s="12" t="inlineStr">
+      <c r="E370" s="14" t="inlineStr">
         <is>
           <t>moe.gate.add</t>
         </is>
       </c>
-      <c r="F370" s="12" t="inlineStr">
+      <c r="F370" s="14" t="inlineStr">
         <is>
           <t>[128, 256], [1, 256]</t>
         </is>
       </c>
-      <c r="G370" s="12" t="inlineStr">
+      <c r="G370" s="14" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H370" s="12" t="inlineStr">
+      <c r="H370" s="14" t="inlineStr">
         <is>
           <t>[128, 256]</t>
         </is>
       </c>
-      <c r="I370" s="12" t="inlineStr">
+      <c r="I370" s="14" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="11" t="n">
+      <c r="A371" s="13" t="n">
         <v>369</v>
       </c>
-      <c r="B371" s="12" t="inlineStr">
+      <c r="B371" s="14" t="inlineStr">
         <is>
           <t>aten.topk.default</t>
         </is>
       </c>
-      <c r="C371" s="12" t="inlineStr">
+      <c r="C371" s="14" t="inlineStr">
         <is>
           <t>model.layers.3.mlp.gate</t>
         </is>
       </c>
-      <c r="D371" s="12" t="inlineStr">
+      <c r="D371" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E371" s="12" t="inlineStr">
+      <c r="E371" s="14" t="inlineStr">
         <is>
           <t>moe.gate.topk</t>
         </is>
       </c>
-      <c r="F371" s="12" t="inlineStr">
+      <c r="F371" s="14" t="inlineStr">
         <is>
           <t>[128, 8, 32]</t>
         </is>
       </c>
-      <c r="G371" s="12" t="inlineStr">
-        <is>
-          <t>torch.float32</t>
-        </is>
-      </c>
-      <c r="H371" s="12" t="inlineStr">
+      <c r="G371" s="14" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H371" s="14" t="inlineStr">
         <is>
           <t>[128, 8, 2], [128, 8, 2]</t>
         </is>
       </c>
-      <c r="I371" s="12" t="inlineStr">
+      <c r="I371" s="14" t="inlineStr">
         <is>
           <t>torch.float32, torch.int64</t>
         </is>
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="11" t="n">
+      <c r="A372" s="13" t="n">
         <v>370</v>
       </c>
-      <c r="B372" s="12" t="inlineStr">
+      <c r="B372" s="14" t="inlineStr">
         <is>
           <t>aten.sum.dim_IntList</t>
         </is>
       </c>
-      <c r="C372" s="12" t="inlineStr">
+      <c r="C372" s="14" t="inlineStr">
         <is>
           <t>model.layers.3.mlp.gate</t>
         </is>
       </c>
-      <c r="D372" s="12" t="inlineStr">
+      <c r="D372" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E372" s="12" t="inlineStr">
+      <c r="E372" s="14" t="inlineStr">
         <is>
           <t>moe.gate.sum</t>
         </is>
       </c>
-      <c r="F372" s="12" t="inlineStr">
+      <c r="F372" s="14" t="inlineStr">
         <is>
           <t>[128, 8, 2]</t>
         </is>
       </c>
-      <c r="G372" s="12" t="inlineStr">
-        <is>
-          <t>torch.float32</t>
-        </is>
-      </c>
-      <c r="H372" s="12" t="inlineStr">
+      <c r="G372" s="14" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H372" s="14" t="inlineStr">
         <is>
           <t>[128, 8]</t>
         </is>
       </c>
-      <c r="I372" s="12" t="inlineStr">
+      <c r="I372" s="14" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="11" t="n">
+      <c r="A373" s="13" t="n">
         <v>371</v>
       </c>
-      <c r="B373" s="12" t="inlineStr">
+      <c r="B373" s="14" t="inlineStr">
         <is>
           <t>aten.topk.default</t>
         </is>
       </c>
-      <c r="C373" s="12" t="inlineStr">
+      <c r="C373" s="14" t="inlineStr">
         <is>
           <t>model.layers.3.mlp.gate</t>
         </is>
       </c>
-      <c r="D373" s="12" t="inlineStr">
+      <c r="D373" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E373" s="12" t="inlineStr">
+      <c r="E373" s="14" t="inlineStr">
         <is>
           <t>moe.gate.topk</t>
         </is>
       </c>
-      <c r="F373" s="12" t="inlineStr">
+      <c r="F373" s="14" t="inlineStr">
         <is>
           <t>[128, 8]</t>
         </is>
       </c>
-      <c r="G373" s="12" t="inlineStr">
-        <is>
-          <t>torch.float32</t>
-        </is>
-      </c>
-      <c r="H373" s="12" t="inlineStr">
+      <c r="G373" s="14" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H373" s="14" t="inlineStr">
         <is>
           <t>[128, 4], [128, 4]</t>
         </is>
       </c>
-      <c r="I373" s="12" t="inlineStr">
+      <c r="I373" s="14" t="inlineStr">
         <is>
           <t>torch.float32, torch.int64</t>
         </is>
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="11" t="n">
+      <c r="A374" s="13" t="n">
         <v>372</v>
       </c>
-      <c r="B374" s="12" t="inlineStr">
+      <c r="B374" s="14" t="inlineStr">
         <is>
           <t>aten._to_copy.default</t>
         </is>
       </c>
-      <c r="C374" s="12" t="inlineStr">
+      <c r="C374" s="14" t="inlineStr">
         <is>
           <t>model.layers.3.mlp.gate</t>
         </is>
       </c>
-      <c r="D374" s="12" t="inlineStr">
+      <c r="D374" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E374" s="12" t="inlineStr">
+      <c r="E374" s="14" t="inlineStr">
         <is>
           <t>moe.gate._to_copy</t>
         </is>
       </c>
-      <c r="F374" s="12" t="inlineStr">
+      <c r="F374" s="14" t="inlineStr">
         <is>
           <t>[128, 256]</t>
         </is>
       </c>
-      <c r="G374" s="12" t="inlineStr">
-        <is>
-          <t>torch.float32</t>
-        </is>
-      </c>
-      <c r="H374" s="12" t="inlineStr">
+      <c r="G374" s="14" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H374" s="14" t="inlineStr">
         <is>
           <t>[128, 256]</t>
         </is>
       </c>
-      <c r="I374" s="12" t="inlineStr">
+      <c r="I374" s="14" t="inlineStr">
         <is>
           <t>torch.bool</t>
         </is>
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="11" t="n">
+      <c r="A375" s="13" t="n">
         <v>373</v>
       </c>
-      <c r="B375" s="12" t="inlineStr">
+      <c r="B375" s="14" t="inlineStr">
         <is>
           <t>aten.masked_fill.Scalar</t>
         </is>
       </c>
-      <c r="C375" s="12" t="inlineStr">
+      <c r="C375" s="14" t="inlineStr">
         <is>
           <t>model.layers.3.mlp.gate</t>
         </is>
       </c>
-      <c r="D375" s="12" t="inlineStr">
+      <c r="D375" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E375" s="12" t="inlineStr">
+      <c r="E375" s="14" t="inlineStr">
         <is>
           <t>moe.gate.masked_fill</t>
         </is>
       </c>
-      <c r="F375" s="12" t="inlineStr">
+      <c r="F375" s="14" t="inlineStr">
         <is>
           <t>[128, 256], [128, 256]</t>
         </is>
       </c>
-      <c r="G375" s="12" t="inlineStr">
+      <c r="G375" s="14" t="inlineStr">
         <is>
           <t>torch.float32, torch.bool</t>
         </is>
       </c>
-      <c r="H375" s="12" t="inlineStr">
+      <c r="H375" s="14" t="inlineStr">
         <is>
           <t>[128, 256]</t>
         </is>
       </c>
-      <c r="I375" s="12" t="inlineStr">
+      <c r="I375" s="14" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="11" t="n">
+      <c r="A376" s="13" t="n">
         <v>374</v>
       </c>
-      <c r="B376" s="12" t="inlineStr">
+      <c r="B376" s="14" t="inlineStr">
         <is>
           <t>aten.topk.default</t>
         </is>
       </c>
-      <c r="C376" s="12" t="inlineStr">
+      <c r="C376" s="14" t="inlineStr">
         <is>
           <t>model.layers.3.mlp.gate</t>
         </is>
       </c>
-      <c r="D376" s="12" t="inlineStr">
+      <c r="D376" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E376" s="12" t="inlineStr">
+      <c r="E376" s="14" t="inlineStr">
         <is>
           <t>moe.gate.topk</t>
         </is>
       </c>
-      <c r="F376" s="12" t="inlineStr">
+      <c r="F376" s="14" t="inlineStr">
         <is>
           <t>[128, 256]</t>
         </is>
       </c>
-      <c r="G376" s="12" t="inlineStr">
-        <is>
-          <t>torch.float32</t>
-        </is>
-      </c>
-      <c r="H376" s="12" t="inlineStr">
+      <c r="G376" s="14" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H376" s="14" t="inlineStr">
         <is>
           <t>[128, 8], [128, 8]</t>
         </is>
       </c>
-      <c r="I376" s="12" t="inlineStr">
+      <c r="I376" s="14" t="inlineStr">
         <is>
           <t>torch.float32, torch.int64</t>
         </is>
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="11" t="n">
+      <c r="A377" s="13" t="n">
         <v>375</v>
       </c>
-      <c r="B377" s="12" t="inlineStr">
+      <c r="B377" s="14" t="inlineStr">
         <is>
           <t>aten.gather.default</t>
         </is>
       </c>
-      <c r="C377" s="12" t="inlineStr">
+      <c r="C377" s="14" t="inlineStr">
         <is>
           <t>model.layers.3.mlp.gate</t>
         </is>
       </c>
-      <c r="D377" s="12" t="inlineStr">
+      <c r="D377" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E377" s="12" t="inlineStr">
+      <c r="E377" s="14" t="inlineStr">
         <is>
           <t>moe.gate.gather</t>
         </is>
       </c>
-      <c r="F377" s="12" t="inlineStr">
+      <c r="F377" s="14" t="inlineStr">
         <is>
           <t>[128, 256], [128, 8]</t>
         </is>
       </c>
-      <c r="G377" s="12" t="inlineStr">
+      <c r="G377" s="14" t="inlineStr">
         <is>
           <t>torch.float32, torch.int64</t>
         </is>
       </c>
-      <c r="H377" s="12" t="inlineStr">
+      <c r="H377" s="14" t="inlineStr">
         <is>
           <t>[128, 8]</t>
         </is>
       </c>
-      <c r="I377" s="12" t="inlineStr">
+      <c r="I377" s="14" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="11" t="n">
+      <c r="A378" s="13" t="n">
         <v>376</v>
       </c>
-      <c r="B378" s="12" t="inlineStr">
+      <c r="B378" s="14" t="inlineStr">
         <is>
           <t>aten.sum.dim_IntList</t>
         </is>
       </c>
-      <c r="C378" s="12" t="inlineStr">
+      <c r="C378" s="14" t="inlineStr">
         <is>
           <t>model.layers.3.mlp.gate</t>
         </is>
       </c>
-      <c r="D378" s="12" t="inlineStr">
+      <c r="D378" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E378" s="12" t="inlineStr">
+      <c r="E378" s="14" t="inlineStr">
         <is>
           <t>moe.gate.sum</t>
         </is>
       </c>
-      <c r="F378" s="12" t="inlineStr">
+      <c r="F378" s="14" t="inlineStr">
         <is>
           <t>[128, 8]</t>
         </is>
       </c>
-      <c r="G378" s="12" t="inlineStr">
-        <is>
-          <t>torch.float32</t>
-        </is>
-      </c>
-      <c r="H378" s="12" t="inlineStr">
+      <c r="G378" s="14" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H378" s="14" t="inlineStr">
         <is>
           <t>[128, 1]</t>
         </is>
       </c>
-      <c r="I378" s="12" t="inlineStr">
+      <c r="I378" s="14" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="11" t="n">
+      <c r="A379" s="13" t="n">
         <v>377</v>
       </c>
-      <c r="B379" s="12" t="inlineStr">
+      <c r="B379" s="14" t="inlineStr">
         <is>
           <t>aten.add.Tensor</t>
         </is>
       </c>
-      <c r="C379" s="12" t="inlineStr">
+      <c r="C379" s="14" t="inlineStr">
         <is>
           <t>model.layers.3.mlp.gate</t>
         </is>
       </c>
-      <c r="D379" s="12" t="inlineStr">
+      <c r="D379" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E379" s="12" t="inlineStr">
+      <c r="E379" s="14" t="inlineStr">
         <is>
           <t>moe.gate.add</t>
         </is>
       </c>
-      <c r="F379" s="12" t="inlineStr">
+      <c r="F379" s="14" t="inlineStr">
         <is>
           <t>[128, 1]</t>
         </is>
       </c>
-      <c r="G379" s="12" t="inlineStr">
-        <is>
-          <t>torch.float32</t>
-        </is>
-      </c>
-      <c r="H379" s="12" t="inlineStr">
+      <c r="G379" s="14" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H379" s="14" t="inlineStr">
         <is>
           <t>[128, 1]</t>
         </is>
       </c>
-      <c r="I379" s="12" t="inlineStr">
+      <c r="I379" s="14" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="11" t="n">
+      <c r="A380" s="13" t="n">
         <v>378</v>
       </c>
-      <c r="B380" s="12" t="inlineStr">
+      <c r="B380" s="14" t="inlineStr">
         <is>
           <t>aten.div.Tensor</t>
         </is>
       </c>
-      <c r="C380" s="12" t="inlineStr">
+      <c r="C380" s="14" t="inlineStr">
         <is>
           <t>model.layers.3.mlp.gate</t>
         </is>
       </c>
-      <c r="D380" s="12" t="inlineStr">
+      <c r="D380" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E380" s="12" t="inlineStr">
+      <c r="E380" s="14" t="inlineStr">
         <is>
           <t>moe.gate.div</t>
         </is>
       </c>
-      <c r="F380" s="12" t="inlineStr">
+      <c r="F380" s="14" t="inlineStr">
         <is>
           <t>[128, 8], [128, 1]</t>
         </is>
       </c>
-      <c r="G380" s="12" t="inlineStr">
+      <c r="G380" s="14" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H380" s="12" t="inlineStr">
+      <c r="H380" s="14" t="inlineStr">
         <is>
           <t>[128, 8]</t>
         </is>
       </c>
-      <c r="I380" s="12" t="inlineStr">
+      <c r="I380" s="14" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="11" t="n">
+      <c r="A381" s="13" t="n">
         <v>379</v>
       </c>
-      <c r="B381" s="12" t="inlineStr">
+      <c r="B381" s="14" t="inlineStr">
         <is>
           <t>aten.mul.Tensor</t>
         </is>
       </c>
-      <c r="C381" s="12" t="inlineStr">
+      <c r="C381" s="14" t="inlineStr">
         <is>
           <t>model.layers.3.mlp.gate</t>
         </is>
       </c>
-      <c r="D381" s="12" t="inlineStr">
+      <c r="D381" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E381" s="12" t="inlineStr">
+      <c r="E381" s="14" t="inlineStr">
         <is>
           <t>moe.gate.mul</t>
         </is>
       </c>
-      <c r="F381" s="12" t="inlineStr">
+      <c r="F381" s="14" t="inlineStr">
         <is>
           <t>[128, 8]</t>
         </is>
       </c>
-      <c r="G381" s="12" t="inlineStr">
-        <is>
-          <t>torch.float32</t>
-        </is>
-      </c>
-      <c r="H381" s="12" t="inlineStr">
+      <c r="G381" s="14" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H381" s="14" t="inlineStr">
         <is>
           <t>[128, 8]</t>
         </is>
       </c>
-      <c r="I381" s="12" t="inlineStr">
+      <c r="I381" s="14" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="15" t="n">
+      <c r="A382" s="17" t="n">
         <v>380</v>
       </c>
-      <c r="B382" s="16" t="inlineStr">
+      <c r="B382" s="18" t="inlineStr">
         <is>
           <t>aten.mm.default</t>
         </is>
       </c>
-      <c r="C382" s="16" t="inlineStr">
+      <c r="C382" s="18" t="inlineStr">
         <is>
           <t>model.layers.3.mlp.experts.0.gate_proj</t>
         </is>
       </c>
-      <c r="D382" s="16" t="inlineStr">
+      <c r="D382" s="18" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E382" s="16" t="inlineStr">
+      <c r="E382" s="18" t="inlineStr">
         <is>
           <t>moe.experts.mm</t>
         </is>
       </c>
-      <c r="F382" s="16" t="inlineStr">
+      <c r="F382" s="18" t="inlineStr">
         <is>
           <t>[128, 7168], [7168, 2048]</t>
         </is>
       </c>
-      <c r="G382" s="16" t="inlineStr">
+      <c r="G382" s="18" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H382" s="16" t="inlineStr">
+      <c r="H382" s="18" t="inlineStr">
         <is>
           <t>[128, 2048]</t>
         </is>
       </c>
-      <c r="I382" s="16" t="inlineStr">
+      <c r="I382" s="18" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="15" t="n">
+      <c r="A383" s="17" t="n">
         <v>381</v>
       </c>
-      <c r="B383" s="16" t="inlineStr">
+      <c r="B383" s="18" t="inlineStr">
         <is>
           <t>aten.silu.default</t>
         </is>
       </c>
-      <c r="C383" s="16" t="inlineStr">
+      <c r="C383" s="18" t="inlineStr">
         <is>
           <t>model.layers.3.mlp.experts.0.act_fn</t>
         </is>
       </c>
-      <c r="D383" s="16" t="inlineStr">
+      <c r="D383" s="18" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E383" s="16" t="inlineStr">
+      <c r="E383" s="18" t="inlineStr">
         <is>
           <t>moe.experts.silu</t>
         </is>
       </c>
-      <c r="F383" s="16" t="inlineStr">
+      <c r="F383" s="18" t="inlineStr">
         <is>
           <t>[128, 2048]</t>
         </is>
       </c>
-      <c r="G383" s="16" t="inlineStr">
-        <is>
-          <t>torch.float32</t>
-        </is>
-      </c>
-      <c r="H383" s="16" t="inlineStr">
+      <c r="G383" s="18" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H383" s="18" t="inlineStr">
         <is>
           <t>[128, 2048]</t>
         </is>
       </c>
-      <c r="I383" s="16" t="inlineStr">
+      <c r="I383" s="18" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="15" t="n">
+      <c r="A384" s="17" t="n">
         <v>382</v>
       </c>
-      <c r="B384" s="16" t="inlineStr">
+      <c r="B384" s="18" t="inlineStr">
         <is>
           <t>aten.mm.default</t>
         </is>
       </c>
-      <c r="C384" s="16" t="inlineStr">
+      <c r="C384" s="18" t="inlineStr">
         <is>
           <t>model.layers.3.mlp.experts.0.up_proj</t>
         </is>
       </c>
-      <c r="D384" s="16" t="inlineStr">
+      <c r="D384" s="18" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E384" s="16" t="inlineStr">
+      <c r="E384" s="18" t="inlineStr">
         <is>
           <t>moe.experts.mm</t>
         </is>
       </c>
-      <c r="F384" s="16" t="inlineStr">
+      <c r="F384" s="18" t="inlineStr">
         <is>
           <t>[128, 7168], [7168, 2048]</t>
         </is>
       </c>
-      <c r="G384" s="16" t="inlineStr">
+      <c r="G384" s="18" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H384" s="16" t="inlineStr">
+      <c r="H384" s="18" t="inlineStr">
         <is>
           <t>[128, 2048]</t>
         </is>
       </c>
-      <c r="I384" s="16" t="inlineStr">
+      <c r="I384" s="18" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="15" t="n">
+      <c r="A385" s="17" t="n">
         <v>383</v>
       </c>
-      <c r="B385" s="16" t="inlineStr">
+      <c r="B385" s="18" t="inlineStr">
         <is>
           <t>aten.mul.Tensor</t>
         </is>
       </c>
-      <c r="C385" s="16" t="inlineStr">
+      <c r="C385" s="18" t="inlineStr">
         <is>
           <t>model.layers.3.mlp.experts.0</t>
         </is>
       </c>
-      <c r="D385" s="16" t="inlineStr">
+      <c r="D385" s="18" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E385" s="16" t="inlineStr">
+      <c r="E385" s="18" t="inlineStr">
         <is>
           <t>moe.experts.mul</t>
         </is>
       </c>
-      <c r="F385" s="16" t="inlineStr">
+      <c r="F385" s="18" t="inlineStr">
         <is>
           <t>[128, 2048], [128, 2048]</t>
         </is>
       </c>
-      <c r="G385" s="16" t="inlineStr">
+      <c r="G385" s="18" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H385" s="16" t="inlineStr">
+      <c r="H385" s="18" t="inlineStr">
         <is>
           <t>[128, 2048]</t>
         </is>
       </c>
-      <c r="I385" s="16" t="inlineStr">
+      <c r="I385" s="18" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="15" t="n">
+      <c r="A386" s="17" t="n">
         <v>384</v>
       </c>
-      <c r="B386" s="16" t="inlineStr">
+      <c r="B386" s="18" t="inlineStr">
         <is>
           <t>aten.mm.default</t>
         </is>
       </c>
-      <c r="C386" s="16" t="inlineStr">
+      <c r="C386" s="18" t="inlineStr">
         <is>
           <t>model.layers.3.mlp.experts.0.down_proj</t>
         </is>
       </c>
-      <c r="D386" s="16" t="inlineStr">
+      <c r="D386" s="18" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E386" s="16" t="inlineStr">
+      <c r="E386" s="18" t="inlineStr">
         <is>
           <t>moe.experts.mm</t>
         </is>
       </c>
-      <c r="F386" s="16" t="inlineStr">
+      <c r="F386" s="18" t="inlineStr">
         <is>
           <t>[128, 2048], [2048, 7168]</t>
         </is>
       </c>
-      <c r="G386" s="16" t="inlineStr">
+      <c r="G386" s="18" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H386" s="16" t="inlineStr">
+      <c r="H386" s="18" t="inlineStr">
         <is>
           <t>[128, 7168]</t>
         </is>
       </c>
-      <c r="I386" s="16" t="inlineStr">
+      <c r="I386" s="18" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="13" t="n">
+      <c r="A387" s="15" t="n">
         <v>385</v>
       </c>
-      <c r="B387" s="14" t="inlineStr">
+      <c r="B387" s="16" t="inlineStr">
         <is>
           <t>aten.mul.Tensor</t>
         </is>
       </c>
-      <c r="C387" s="14" t="inlineStr">
+      <c r="C387" s="16" t="inlineStr">
         <is>
           <t>model.layers.3.mlp</t>
         </is>
       </c>
-      <c r="D387" s="14" t="inlineStr">
+      <c r="D387" s="16" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E387" s="14" t="inlineStr">
+      <c r="E387" s="16" t="inlineStr">
         <is>
           <t>ffn.mul</t>
         </is>
       </c>
-      <c r="F387" s="14" t="inlineStr">
+      <c r="F387" s="16" t="inlineStr">
         <is>
           <t>[128, 7168], [128, 1]</t>
         </is>
       </c>
-      <c r="G387" s="14" t="inlineStr">
+      <c r="G387" s="16" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H387" s="14" t="inlineStr">
+      <c r="H387" s="16" t="inlineStr">
         <is>
           <t>[128, 7168]</t>
         </is>
       </c>
-      <c r="I387" s="14" t="inlineStr">
+      <c r="I387" s="16" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="17" t="n">
+      <c r="A388" s="19" t="n">
         <v>386</v>
       </c>
-      <c r="B388" s="18" t="inlineStr">
+      <c r="B388" s="20" t="inlineStr">
         <is>
           <t>aten.mm.default</t>
         </is>
       </c>
-      <c r="C388" s="18" t="inlineStr">
+      <c r="C388" s="20" t="inlineStr">
         <is>
           <t>model.layers.3.mlp.shared_experts.gate_proj</t>
         </is>
       </c>
-      <c r="D388" s="18" t="inlineStr">
+      <c r="D388" s="20" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E388" s="18" t="inlineStr">
+      <c r="E388" s="20" t="inlineStr">
         <is>
           <t>moe.shared.gate_proj</t>
         </is>
       </c>
-      <c r="F388" s="18" t="inlineStr">
+      <c r="F388" s="20" t="inlineStr">
         <is>
           <t>[128, 7168], [7168, 2048]</t>
         </is>
       </c>
-      <c r="G388" s="18" t="inlineStr">
+      <c r="G388" s="20" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H388" s="18" t="inlineStr">
+      <c r="H388" s="20" t="inlineStr">
         <is>
           <t>[128, 2048]</t>
         </is>
       </c>
-      <c r="I388" s="18" t="inlineStr">
+      <c r="I388" s="20" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="17" t="n">
+      <c r="A389" s="19" t="n">
         <v>387</v>
       </c>
-      <c r="B389" s="18" t="inlineStr">
+      <c r="B389" s="20" t="inlineStr">
         <is>
           <t>aten.silu.default</t>
         </is>
       </c>
-      <c r="C389" s="18" t="inlineStr">
+      <c r="C389" s="20" t="inlineStr">
         <is>
           <t>model.layers.3.mlp.shared_experts.act_fn</t>
         </is>
       </c>
-      <c r="D389" s="18" t="inlineStr">
+      <c r="D389" s="20" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E389" s="18" t="inlineStr">
+      <c r="E389" s="20" t="inlineStr">
         <is>
           <t>moe.shared.silu</t>
         </is>
       </c>
-      <c r="F389" s="18" t="inlineStr">
+      <c r="F389" s="20" t="inlineStr">
         <is>
           <t>[1, 128, 2048]</t>
         </is>
       </c>
-      <c r="G389" s="18" t="inlineStr">
-        <is>
-          <t>torch.float32</t>
-        </is>
-      </c>
-      <c r="H389" s="18" t="inlineStr">
+      <c r="G389" s="20" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="H389" s="20" t="inlineStr">
         <is>
           <t>[1, 128, 2048]</t>
         </is>
       </c>
-      <c r="I389" s="18" t="inlineStr">
+      <c r="I389" s="20" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="17" t="n">
+      <c r="A390" s="19" t="n">
         <v>388</v>
       </c>
-      <c r="B390" s="18" t="inlineStr">
+      <c r="B390" s="20" t="inlineStr">
         <is>
           <t>aten.mm.default</t>
         </is>
       </c>
-      <c r="C390" s="18" t="inlineStr">
+      <c r="C390" s="20" t="inlineStr">
         <is>
           <t>model.layers.3.mlp.shared_experts.up_proj</t>
         </is>
       </c>
-      <c r="D390" s="18" t="inlineStr">
+      <c r="D390" s="20" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E390" s="18" t="inlineStr">
+      <c r="E390" s="20" t="inlineStr">
         <is>
           <t>moe.shared.up_proj</t>
         </is>
       </c>
-      <c r="F390" s="18" t="inlineStr">
+      <c r="F390" s="20" t="inlineStr">
         <is>
           <t>[128, 7168], [7168, 2048]</t>
         </is>
       </c>
-      <c r="G390" s="18" t="inlineStr">
+      <c r="G390" s="20" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H390" s="18" t="inlineStr">
+      <c r="H390" s="20" t="inlineStr">
         <is>
           <t>[128, 2048]</t>
         </is>
       </c>
-      <c r="I390" s="18" t="inlineStr">
+      <c r="I390" s="20" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="17" t="n">
+      <c r="A391" s="19" t="n">
         <v>389</v>
       </c>
-      <c r="B391" s="18" t="inlineStr">
+      <c r="B391" s="20" t="inlineStr">
         <is>
           <t>aten.mul.Tensor</t>
         </is>
       </c>
-      <c r="C391" s="18" t="inlineStr">
+      <c r="C391" s="20" t="inlineStr">
         <is>
           <t>model.layers.3.mlp.shared_experts</t>
         </is>
       </c>
-      <c r="D391" s="18" t="inlineStr">
+      <c r="D391" s="20" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E391" s="18" t="inlineStr">
+      <c r="E391" s="20" t="inlineStr">
         <is>
           <t>moe.shared.mul</t>
         </is>
       </c>
-      <c r="F391" s="18" t="inlineStr">
+      <c r="F391" s="20" t="inlineStr">
         <is>
           <t>[1, 128, 2048], [1, 128, 2048]</t>
         </is>
       </c>
-      <c r="G391" s="18" t="inlineStr">
+      <c r="G391" s="20" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H391" s="18" t="inlineStr">
+      <c r="H391" s="20" t="inlineStr">
         <is>
           <t>[1, 128, 2048]</t>
         </is>
       </c>
-      <c r="I391" s="18" t="inlineStr">
+      <c r="I391" s="20" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="17" t="n">
+      <c r="A392" s="19" t="n">
         <v>390</v>
       </c>
-      <c r="B392" s="18" t="inlineStr">
+      <c r="B392" s="20" t="inlineStr">
         <is>
           <t>aten.mm.default</t>
         </is>
       </c>
-      <c r="C392" s="18" t="inlineStr">
+      <c r="C392" s="20" t="inlineStr">
         <is>
           <t>model.layers.3.mlp.shared_experts.down_proj</t>
         </is>
       </c>
-      <c r="D392" s="18" t="inlineStr">
+      <c r="D392" s="20" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E392" s="18" t="inlineStr">
+      <c r="E392" s="20" t="inlineStr">
         <is>
           <t>moe.shared.down_proj</t>
         </is>
       </c>
-      <c r="F392" s="18" t="inlineStr">
+      <c r="F392" s="20" t="inlineStr">
         <is>
           <t>[128, 2048], [2048, 7168]</t>
         </is>
       </c>
-      <c r="G392" s="18" t="inlineStr">
+      <c r="G392" s="20" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H392" s="18" t="inlineStr">
+      <c r="H392" s="20" t="inlineStr">
         <is>
           <t>[128, 7168]</t>
         </is>
       </c>
-      <c r="I392" s="18" t="inlineStr">
+      <c r="I392" s="20" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="13" t="n">
+      <c r="A393" s="15" t="n">
         <v>391</v>
       </c>
-      <c r="B393" s="14" t="inlineStr">
+      <c r="B393" s="16" t="inlineStr">
         <is>
           <t>aten.add.Tensor</t>
         </is>
       </c>
-      <c r="C393" s="14" t="inlineStr">
+      <c r="C393" s="16" t="inlineStr">
         <is>
           <t>model.layers.3.mlp</t>
         </is>
       </c>
-      <c r="D393" s="14" t="inlineStr">
+      <c r="D393" s="16" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E393" s="14" t="inlineStr">
+      <c r="E393" s="16" t="inlineStr">
         <is>
           <t>ffn.add</t>
         </is>
       </c>
-      <c r="F393" s="14" t="inlineStr">
+      <c r="F393" s="16" t="inlineStr">
         <is>
           <t>[1, 128, 7168], [1, 128, 7168]</t>
         </is>
       </c>
-      <c r="G393" s="14" t="inlineStr">
+      <c r="G393" s="16" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H393" s="14" t="inlineStr">
+      <c r="H393" s="16" t="inlineStr">
         <is>
           <t>[1, 128, 7168]</t>
         </is>
       </c>
-      <c r="I393" s="14" t="inlineStr">
+      <c r="I393" s="16" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="5" t="n">
+      <c r="A394" s="11" t="n">
         <v>392</v>
       </c>
-      <c r="B394" s="6" t="inlineStr">
+      <c r="B394" s="12" t="inlineStr">
         <is>
           <t>aten.add.Tensor</t>
         </is>
       </c>
-      <c r="C394" s="6" t="inlineStr">
+      <c r="C394" s="12" t="inlineStr">
         <is>
           <t>model.layers.3</t>
         </is>
       </c>
-      <c r="D394" s="6" t="inlineStr">
+      <c r="D394" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E394" s="6" t="inlineStr">
+      <c r="E394" s="12" t="inlineStr">
         <is>
           <t>add</t>
         </is>
       </c>
-      <c r="F394" s="6" t="inlineStr">
+      <c r="F394" s="12" t="inlineStr">
         <is>
           <t>[1, 128, 7168], [1, 128, 7168]</t>
         </is>
       </c>
-      <c r="G394" s="6" t="inlineStr">
+      <c r="G394" s="12" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H394" s="6" t="inlineStr">
+      <c r="H394" s="12" t="inlineStr">
         <is>
           <t>[1, 128, 7168]</t>
         </is>
       </c>
-      <c r="I394" s="6" t="inlineStr">
+      <c r="I394" s="12" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
@@ -18699,41 +22748,41 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="3" t="n">
+      <c r="A401" s="5" t="n">
         <v>399</v>
       </c>
-      <c r="B401" s="4" t="inlineStr">
+      <c r="B401" s="6" t="inlineStr">
         <is>
           <t>aten.mm.default</t>
         </is>
       </c>
-      <c r="C401" s="4" t="inlineStr">
+      <c r="C401" s="6" t="inlineStr">
         <is>
           <t>lm_head</t>
         </is>
       </c>
-      <c r="D401" s="4" t="inlineStr"/>
-      <c r="E401" s="4" t="inlineStr">
+      <c r="D401" s="6" t="inlineStr"/>
+      <c r="E401" s="6" t="inlineStr">
         <is>
           <t>lm_head</t>
         </is>
       </c>
-      <c r="F401" s="4" t="inlineStr">
+      <c r="F401" s="6" t="inlineStr">
         <is>
           <t>[128, 7168], [7168, 129280]</t>
         </is>
       </c>
-      <c r="G401" s="4" t="inlineStr">
+      <c r="G401" s="6" t="inlineStr">
         <is>
           <t>torch.float32, torch.float32</t>
         </is>
       </c>
-      <c r="H401" s="4" t="inlineStr">
+      <c r="H401" s="6" t="inlineStr">
         <is>
           <t>[128, 129280]</t>
         </is>
       </c>
-      <c r="I401" s="4" t="inlineStr">
+      <c r="I401" s="6" t="inlineStr">
         <is>
           <t>torch.float32</t>
         </is>
@@ -18741,536 +22790,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I401"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>_to_copy</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>add</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>attn.add</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>attn.cat</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>attn.copy_</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>attn.index</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>attn.kv_a_proj</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>attn.kv_b_proj</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>attn.kv_norm</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>attn.mul</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>attn.neg</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>attn.new_empty</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>attn.o_proj</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>attn.q_a_proj</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>attn.q_b_proj</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>attn.q_norm</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>attn.rope</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>attn.score</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>attn.softmax</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>attn.transpose</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>attn_norm</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>embedding</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>ffn.add</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>ffn.down_proj</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>ffn.mul</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>ffn.silu</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>ffn.up_proj</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>ffn_norm</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>final_norm</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>lm_head</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>masked_fill</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>moe.experts.mm</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>moe.experts.mul</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>moe.experts.silu</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>moe.gate._to_copy</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>moe.gate.add</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>moe.gate.div</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>moe.gate.gather</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>moe.gate.masked_fill</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>moe.gate.mm</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>moe.gate.mul</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>moe.gate.sigmoid</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>moe.gate.sum</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>moe.gate.topk</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>moe.shared.down_proj</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>moe.shared.gate_proj</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>moe.shared.mul</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>moe.shared.silu</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>moe.shared.up_proj</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>rsub</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19281,103 +22800,910 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Fused Operator</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Op Count</t>
+          <t>Count</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Components</t>
+          <t>Avg Sub-ops</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>input_layernorm (DeepseekV3RMSNorm)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>92</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>add, attn.add, attn.cat, attn.copy_, attn.index, attn.kv_a_proj, attn.kv_b_proj, attn.kv_norm, attn.mul, attn.neg, attn.new_empty, attn.o_proj, attn.q_a_proj, attn.q_b_proj, attn.q_norm, attn.rope, attn.score, attn.softmax, attn.transpose, attn_norm, ffn.down_proj, ffn.mul, ffn.silu, ffn.up_proj, ffn_norm, moe.gate.mm</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="C2" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>lm_head</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>92</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>add, attn.add, attn.cat, attn.copy_, attn.index, attn.kv_a_proj, attn.kv_b_proj, attn.kv_norm, attn.mul, attn.neg, attn.new_empty, attn.o_proj, attn.q_a_proj, attn.q_b_proj, attn.q_norm, attn.rope, attn.score, attn.softmax, attn.transpose, attn_norm, ffn.down_proj, ffn.mul, ffn.silu, ffn.up_proj, ffn_norm, moe.gate.mm</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>mlp</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>92</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>add, attn.add, attn.cat, attn.copy_, attn.index, attn.kv_a_proj, attn.kv_b_proj, attn.kv_norm, attn.mul, attn.neg, attn.new_empty, attn.o_proj, attn.q_a_proj, attn.q_b_proj, attn.q_norm, attn.rope, attn.score, attn.softmax, attn.transpose, attn_norm, ffn.down_proj, ffn.mul, ffn.silu, ffn.up_proj, ffn_norm, moe.gate.mm</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>mlp (DeepseekV3MLP)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>113</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>add, attn.add, attn.cat, attn.copy_, attn.index, attn.kv_a_proj, attn.kv_b_proj, attn.kv_norm, attn.mul, attn.neg, attn.new_empty, attn.o_proj, attn.q_a_proj, attn.q_b_proj, attn.q_norm, attn.rope, attn.score, attn.softmax, attn.transpose, attn_norm, ffn.add, ffn.mul, ffn_norm, moe.experts.mm, moe.experts.mul, moe.experts.silu, moe.gate._to_copy, moe.gate.add, moe.gate.div, moe.gate.gather, moe.gate.masked_fill, moe.gate.mm, moe.gate.mul, moe.gate.sigmoid, moe.gate.sum, moe.gate.topk, moe.shared.down_proj, moe.shared.gate_proj, moe.shared.mul, moe.shared.silu, moe.shared.up_proj</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>mlp.experts.0 (DeepseekV3MLP)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mlp.gate (MoEGate)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>mlp.shared_experts (DeepseekV3MLP)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>model (DeepseekV3Model)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>model.layers.0</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>model.layers.1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>model.layers.2</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>model.layers.3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>model.norm (DeepseekV3RMSNorm)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>post_attention_layernorm (DeepseekV3RMSNorm)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>self_attn</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>12</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>self_attn (DeepseekV3Attention)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>self_attn.kv_a_layernorm (DeepseekV3RMSNorm)</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>self_attn.kv_a_proj_with_mqa</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>self_attn.kv_b_proj</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>self_attn.o_proj</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>self_attn.q_a_layernorm (DeepseekV3RMSNorm)</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>self_attn.q_a_proj</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>self_attn.q_b_proj</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>self_attn.rotary_emb (DeepseekV3YarnRotaryEmbedding)</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="n">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="100" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fused Op Count</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Raw Op Count</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Fused Operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C2" t="n">
+        <v>92</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>input_layernorm (DeepseekV3RMSNorm), self_attn.q_a_proj, self_attn.q_a_layernorm (DeepseekV3RMSNorm), self_attn.q_b_proj, self_attn, self_attn.kv_a_proj_with_mqa, self_attn.kv_a_layernorm (DeepseekV3RMSNorm), self_attn.kv_b_proj, self_attn.rotary_emb (DeepseekV3YarnRotaryEmbedding), self_attn (DeepseekV3Attention), self_attn.o_proj, model.layers.0, post_attention_layernorm (DeepseekV3RMSNorm), mlp (DeepseekV3MLP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C3" t="n">
+        <v>92</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>input_layernorm (DeepseekV3RMSNorm), self_attn.q_a_proj, self_attn.q_a_layernorm (DeepseekV3RMSNorm), self_attn.q_b_proj, self_attn, self_attn.kv_a_proj_with_mqa, self_attn.kv_a_layernorm (DeepseekV3RMSNorm), self_attn.kv_b_proj, self_attn.rotary_emb (DeepseekV3YarnRotaryEmbedding), self_attn (DeepseekV3Attention), self_attn.o_proj, model.layers.1, post_attention_layernorm (DeepseekV3RMSNorm), mlp (DeepseekV3MLP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>17</v>
+      </c>
+      <c r="C4" t="n">
+        <v>92</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>input_layernorm (DeepseekV3RMSNorm), self_attn.q_a_proj, self_attn.q_a_layernorm (DeepseekV3RMSNorm), self_attn.q_b_proj, self_attn, self_attn.kv_a_proj_with_mqa, self_attn.kv_a_layernorm (DeepseekV3RMSNorm), self_attn.kv_b_proj, self_attn.rotary_emb (DeepseekV3YarnRotaryEmbedding), self_attn (DeepseekV3Attention), self_attn.o_proj, model.layers.2, post_attention_layernorm (DeepseekV3RMSNorm), mlp (DeepseekV3MLP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>21</v>
+      </c>
+      <c r="C5" t="n">
+        <v>113</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>input_layernorm (DeepseekV3RMSNorm), self_attn.q_a_proj, self_attn.q_a_layernorm (DeepseekV3RMSNorm), self_attn.q_b_proj, self_attn, self_attn.kv_a_proj_with_mqa, self_attn.kv_a_layernorm (DeepseekV3RMSNorm), self_attn.kv_b_proj, self_attn.rotary_emb (DeepseekV3YarnRotaryEmbedding), self_attn (DeepseekV3Attention), self_attn.o_proj, model.layers.3, post_attention_layernorm (DeepseekV3RMSNorm), mlp.gate (MoEGate), mlp.experts.0 (DeepseekV3MLP), mlp, mlp.shared_experts (DeepseekV3MLP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>non-layer</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
         <v>11</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>_to_copy, embedding, final_norm, lm_head, masked_fill, rsub</t>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>model (DeepseekV3Model), model.norm (DeepseekV3RMSNorm), lm_head</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
+    <col width="55" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="65" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Module Class</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Fusion Level</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Aten Op Sequence</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Sub-ops</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Occurrences</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Example Module Path</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Fused Input Shapes</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Fused Input Dtypes</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Input Sources</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Fused Output Shapes</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Fused Output Dtypes</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Output Sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>DeepseekV3RMSNorm</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>leaf</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar → aten.mean.dim → aten.add.Tensor → aten.rsqrt.default → aten.mul.Tensor</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>model.layers.0.input_layernorm</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168], [7168]</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>aten.pow.Tensor_Scalar (in[0]) | aten.mul.Tensor (in[0])</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168]</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>DeepseekV3MLP</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>parent</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default → aten.silu.default → aten.mul.Tensor</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>model.layers.0.mlp</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>[7168, 18432], [1, 128, 18432]</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (in[1]) | aten.mul.Tensor (in[1])</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>[128, 18432], [128, 7168]</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (out[0]) | aten.mm.default (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>DeepseekV3YarnRotaryEmbedding</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>leaf</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>aten.arange.start_step → aten.div.Tensor → aten.pow.Scalar → aten.reciprocal.default → aten.mul.Tensor → aten.sub.Tensor → aten.clamp.default → aten._to_copy.default → aten.rsub.Scalar → aten.add.Tensor → aten.cat.default → aten.cos.default → aten.sin.default</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>model.layers.0.self_attn.rotary_emb</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>[128, 1]</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor (in[0])</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>[128, 64], [128, 64]</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>aten.mul.Tensor (out[0]) | aten.mul.Tensor (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>DeepseekV3Attention</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>leaf</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>aten.index.Tensor → aten.transpose.int → aten.mul.Tensor → aten.neg.default → aten.cat.default → aten.add.Tensor → aten.new_empty.default → aten.copy_.default → aten.bmm.default → aten._softmax.default</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>model.layers.0.self_attn</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>[128, 64], [1, 128], [128, 64], [1, 128, 128, 64], [1, 1, 128, 64], [1, 128, 128, 32], [1, 128, 128, 32], [1, 1, 128, 64], [1, 1, 128, 32], [1, 1, 128, 32], [1, 128, 128, 128], [1, 128, 128, 128], [1, 128, 128, 64], [1, 128, 128, 128], [1, 1, 128, 128], [128, 128, 128], [1, 128, 128, 128]</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.int64, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>aten.index.Tensor (in[0]) | aten.index.Tensor (in[1]) | aten.index.Tensor (in[0]) | aten.mul.Tensor (in[0]) | aten.mul.Tensor (in[1]) | aten.neg.default (in[0]) | aten.cat.default (in[1]) | aten.mul.Tensor (in[1]) | aten.neg.default (in[0]) | aten.cat.default (in[1]) | aten.copy_.default (in[1]) | aten.copy_.default (in[1]) | aten.copy_.default (in[1]) | aten.mul.Tensor (in[0]) | aten.add.Tensor (in[1]) | aten.bmm.default (in[1]) | aten.transpose.int (in[0])</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 64], [1, 128, 64], [1, 128, 128, 192], [128, 128, 128], [128, 128, 128]</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32, torch.float32, torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>aten.index.Tensor (out[0]) | aten.index.Tensor (out[0]) | aten.new_empty.default (out[0]) | aten.bmm.default (out[0]) | aten.bmm.default (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>DeepseekV3Model</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>parent</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>aten.embedding.default → aten.rsub.Scalar → aten._to_copy.default → aten.masked_fill.Scalar</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>[129280, 7168], [1, 128], [1, 1, 128, 128]</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.int64, torch.float32</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>aten.embedding.default (in[0]) | aten.embedding.default (in[1]) | aten.rsub.Scalar (in[0])</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 7168], [1, 1, 128, 128]</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32, torch.float32</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>aten.embedding.default (out[0]) | aten.masked_fill.Scalar (out[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>MoEGate</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>leaf</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default → aten.sigmoid.default → aten.add.Tensor → aten.topk.default → aten.sum.dim_IntList → aten._to_copy.default → aten.masked_fill.Scalar → aten.gather.default → aten.div.Tensor → aten.mul.Tensor</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>model.layers.3.mlp.gate</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>[128, 7168]</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>torch.float32</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>aten.mm.default (in[0])</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>[128, 4], [128, 256], [128, 8]</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>torch.int64, torch.bool, torch.float32</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>aten.topk.default (out[1]) | aten._to_copy.default (out[0]) | aten.mul.Tensor (out[0])</t>
         </is>
       </c>
     </row>

--- a/deepseek_v3_ops.xlsx
+++ b/deepseek_v3_ops.xlsx
@@ -2641,32 +2641,32 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>[1, 128, 18432]</t>
+          <t>[7168, 18432], [1, 128, 18432]</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>torch.float32</t>
+          <t>torch.float32, torch.float32</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>aten.mul.Tensor (in[1])</t>
+          <t>aten.mm.default (in[1]) | aten.mul.Tensor (in[1])</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>[128, 7168]</t>
+          <t>[128, 18432], [128, 7168]</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>torch.float32</t>
+          <t>torch.float32, torch.float32</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>aten.mm.default (out[0])</t>
+          <t>aten.mm.default (out[0]) | aten.mm.default (out[0])</t>
         </is>
       </c>
     </row>

--- a/deepseek_v3_ops.xlsx
+++ b/deepseek_v3_ops.xlsx
@@ -926,7 +926,7 @@
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>embedding[0] | embedding[1]</t>
+          <t>embedding[0](param:weight) | embedding[1]</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
@@ -965,17 +965,17 @@
       <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>[1, 1, 128, 128], [1, 1, 128, 128], [1, 1, 128, 128]</t>
+          <t>[1, 1, 128, 128], [1, 1, 128, 128]</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>torch.float32, torch.float32, torch.bool</t>
+          <t>torch.float32, torch.float32</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>rsub[0] | _to_copy[0] | masked_fill[1]</t>
+          <t>rsub[0] | _to_copy[0]</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -1018,17 +1018,17 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>[1, 128, 7168], [1, 128, 7168], [1, 128, 1], [1, 128, 7168], [7168]</t>
+          <t>[1, 128, 7168], [1, 128, 7168], [1, 128, 1], [7168]</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>torch.bfloat16, torch.float32, torch.float32, torch.float32, torch.bfloat16</t>
+          <t>torch.bfloat16, torch.float32, torch.float32, torch.bfloat16</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>_to_copy[0] | pow[0] | add[0] | _to_copy[0] | mul[0]</t>
+          <t>_to_copy[0] | pow[0] | add[0] | mul[0](param:weight)</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr"/>
@@ -1112,17 +1112,17 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>[1, 128, 1536], [1, 128, 1536], [1, 128, 1], [1536]</t>
+          <t>[1, 128, 1536], [1, 128, 1536], [1, 128, 1536], [1, 128, 1], [1, 128, 1536], [1536]</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>torch.bfloat16, torch.float32, torch.float32, torch.bfloat16</t>
+          <t>torch.bfloat16, torch.float32, torch.float32, torch.float32, torch.float32, torch.bfloat16</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>_to_copy[0] | pow[0] | add[0] | mul[0]</t>
+          <t>_to_copy[0] | pow[0] | mean[0] | add[0] | _to_copy[0] | mul[0](param:weight)</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr"/>
@@ -1247,17 +1247,17 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>[128, 7168]</t>
+          <t>[128, 7168], [7168, 576]</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>torch.bfloat16</t>
+          <t>torch.bfloat16, torch.bfloat16</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>mm[0]</t>
+          <t>mm[0] | mm[1]</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr"/>
@@ -1341,17 +1341,17 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>[1, 128, 512], [1, 128, 1], [512]</t>
+          <t>[1, 128, 512], [1, 128, 512], [1, 128, 1], [1, 128, 512], [512]</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>torch.bfloat16, torch.float32, torch.bfloat16</t>
+          <t>torch.bfloat16, torch.float32, torch.float32, torch.float32, torch.bfloat16</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>_to_copy[0] | add[0] | mul[0]</t>
+          <t>_to_copy[0] | pow[0] | add[0] | _to_copy[0] | mul[0](param:weight)</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr"/>
@@ -1382,17 +1382,17 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>[128, 512]</t>
+          <t>[128, 512], [512, 32768]</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>torch.bfloat16</t>
+          <t>torch.bfloat16, torch.bfloat16</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>mm[0]</t>
+          <t>mm[0] | mm[1]</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -1448,9 +1448,21 @@
           <t>transpose[0]</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr"/>
-      <c r="J13" s="4" t="inlineStr"/>
-      <c r="K13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>[1, 128, 128, 256]</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>torch.bfloat16</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>transpose[0]</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -1476,22 +1488,34 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>[32], [32], [32], [128, 1], [128, 64]</t>
+          <t>[32], [32], [32], [128, 1], [128, 64], [128, 64]</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>torch.float32, torch.float32, torch.float32, torch.float32, torch.float32</t>
+          <t>torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>reciprocal[0] | div[0] | mul[0] | mul[0] | _to_copy[0]</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr"/>
-      <c r="J14" s="4" t="inlineStr"/>
-      <c r="K14" s="4" t="inlineStr"/>
+          <t>reciprocal[0] | div[0] | mul[0] | mul[0] | cos[0] | _to_copy[0]</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>[128, 64]</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>torch.bfloat16</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>_to_copy[0]</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -1517,32 +1541,32 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>[128, 64], [1, 128], [128, 64], [1, 1, 128, 64], [1, 1, 128, 64], [1, 128, 128, 128], [1, 128, 128, 128], [1, 128, 128, 128], [1, 1, 128, 128], [128, 128, 128]</t>
+          <t>[128, 64], [1, 128], [128, 64], [1, 1, 128, 64], [1, 1, 128, 64], [1, 128, 128, 128], [1, 128, 128, 128], [1, 1, 128, 128], [128, 128, 128]</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>torch.bfloat16, torch.int64, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.float32, torch.bfloat16</t>
+          <t>torch.bfloat16, torch.int64, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.float32, torch.bfloat16</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>index[0] | index[1] | index[0] | mul[0] | new_empty[0] | copy_[1] | copy_[1] | mul[0] | add[1] | bmm[1]</t>
+          <t>index[0] | index[1] | index[0] | mul[0] | new_empty[0] | copy_[1] | mul[0] | add[1] | bmm[1]</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>[1, 128, 128, 192], [1, 128, 128, 128], [128, 128, 128]</t>
+          <t>[1, 128, 128, 128], [128, 128, 128]</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>torch.bfloat16, torch.bfloat16, torch.bfloat16</t>
+          <t>torch.bfloat16, torch.bfloat16</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>new_empty[0] | _to_copy[0] | bmm[0]</t>
+          <t>_to_copy[0] | bmm[0]</t>
         </is>
       </c>
     </row>
@@ -1676,17 +1700,17 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>[1, 128, 7168], [1, 128, 7168], [1, 128, 1], [1, 128, 1], [1, 128, 7168], [7168]</t>
+          <t>[1, 128, 7168], [1, 128, 7168], [1, 128, 1], [1, 128, 7168], [7168]</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>torch.bfloat16, torch.float32, torch.float32, torch.float32, torch.float32, torch.bfloat16</t>
+          <t>torch.bfloat16, torch.float32, torch.float32, torch.float32, torch.bfloat16</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>_to_copy[0] | pow[0] | add[0] | mul[1] | _to_copy[0] | mul[0]</t>
+          <t>_to_copy[0] | pow[0] | rsqrt[0] | _to_copy[0] | mul[0](param:weight)</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr"/>
@@ -2045,7 +2069,7 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>_to_copy[0] | pow[0] | add[0] | mul[0]</t>
+          <t>_to_copy[0] | pow[0] | add[0] | mul[0](param:weight)</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr"/>
@@ -2139,7 +2163,7 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>_to_copy[0] | pow[0] | mean[0] | add[0] | _to_copy[0] | mul[0]</t>
+          <t>_to_copy[0] | pow[0] | mean[0] | add[0] | _to_copy[0] | mul[0](param:weight)</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr"/>
@@ -2264,17 +2288,17 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>[128, 7168], [7168, 576]</t>
+          <t>[128, 7168]</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>torch.bfloat16, torch.bfloat16</t>
+          <t>torch.bfloat16</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>mm[0] | mm[1]</t>
+          <t>mm[0]</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr"/>
@@ -2358,17 +2382,17 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>[1, 128, 512], [1, 128, 512], [1, 128, 1], [1, 128, 512], [512]</t>
+          <t>[1, 128, 512], [1, 128, 512], [512]</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>torch.bfloat16, torch.float32, torch.float32, torch.float32, torch.bfloat16</t>
+          <t>torch.bfloat16, torch.float32, torch.bfloat16</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>_to_copy[0] | pow[0] | add[0] | _to_copy[0] | mul[0]</t>
+          <t>_to_copy[0] | _to_copy[0] | mul[0](param:weight)</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr"/>
@@ -2412,21 +2436,9 @@
           <t>mm[0] | mm[1]</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>[128, 32768]</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>torch.bfloat16</t>
-        </is>
-      </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>mm[0]</t>
-        </is>
-      </c>
+      <c r="I33" s="4" t="inlineStr"/>
+      <c r="J33" s="4" t="inlineStr"/>
+      <c r="K33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
@@ -2465,21 +2477,9 @@
           <t>transpose[0]</t>
         </is>
       </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>[1, 128, 128, 256]</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>torch.bfloat16</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>transpose[0]</t>
-        </is>
-      </c>
+      <c r="I34" s="4" t="inlineStr"/>
+      <c r="J34" s="4" t="inlineStr"/>
+      <c r="K34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
@@ -2505,34 +2505,22 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>[32], [32], [32], [128, 1], [128, 64], [128, 64]</t>
+          <t>[32], [32], [32], [128, 1], [128, 64]</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32</t>
+          <t>torch.float32, torch.float32, torch.float32, torch.float32, torch.float32</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>reciprocal[0] | div[0] | mul[0] | mul[0] | cos[0] | _to_copy[0]</t>
-        </is>
-      </c>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>[128, 64]</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>torch.bfloat16</t>
-        </is>
-      </c>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>_to_copy[0]</t>
-        </is>
-      </c>
+          <t>reciprocal[0] | div[0] | mul[0] | mul[0] | _to_copy[0]</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr"/>
+      <c r="J35" s="4" t="inlineStr"/>
+      <c r="K35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
@@ -2558,17 +2546,17 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>[128, 64], [1, 128], [128, 64], [1, 1, 128, 64], [1, 1, 128, 64], [1, 128, 128, 128], [1, 128, 128, 128], [1, 1, 128, 128], [128, 128, 128]</t>
+          <t>[128, 64], [1, 128], [128, 64], [1, 1, 128, 64], [1, 1, 128, 64], [1, 128, 128, 128], [1, 128, 128, 64], [1, 128, 128, 128], [1, 1, 128, 128], [1, 128, 128, 128]</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>torch.bfloat16, torch.int64, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.float32, torch.bfloat16</t>
+          <t>torch.bfloat16, torch.int64, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.float32, torch.float32</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>index[0] | index[1] | index[0] | mul[0] | new_empty[0] | copy_[1] | mul[0] | add[1] | bmm[1]</t>
+          <t>index[0] | index[1] | index[0] | mul[0] | new_empty[0] | copy_[1] | copy_[1] | mul[0] | add[1] | _softmax[0]</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -2665,21 +2653,9 @@
           <t>add[0]</t>
         </is>
       </c>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>[1, 128, 7168]</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>torch.bfloat16</t>
-        </is>
-      </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>add[0]</t>
-        </is>
-      </c>
+      <c r="I38" s="4" t="inlineStr"/>
+      <c r="J38" s="4" t="inlineStr"/>
+      <c r="K38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
@@ -2715,7 +2691,7 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>_to_copy[0] | pow[0] | rsqrt[0] | _to_copy[0] | mul[0]</t>
+          <t>_to_copy[0] | mean[0] | add[0] | _to_copy[0] | mul[0](param:weight)</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr"/>
@@ -2918,21 +2894,9 @@
           <t>mul[0] | mul[1]</t>
         </is>
       </c>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>[1, 128, 18432]</t>
-        </is>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>torch.bfloat16</t>
-        </is>
-      </c>
-      <c r="K43" s="4" t="inlineStr">
-        <is>
-          <t>mul[0]</t>
-        </is>
-      </c>
+      <c r="I43" s="4" t="inlineStr"/>
+      <c r="J43" s="4" t="inlineStr"/>
+      <c r="K43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
@@ -3064,17 +3028,17 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>[1, 128, 7168], [1, 128, 1], [1, 128, 1], [7168]</t>
+          <t>[1, 128, 7168], [1, 128, 7168], [1, 128, 7168], [1, 128, 1], [1, 128, 7168], [7168]</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>torch.bfloat16, torch.float32, torch.float32, torch.bfloat16</t>
+          <t>torch.bfloat16, torch.float32, torch.float32, torch.float32, torch.float32, torch.bfloat16</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>_to_copy[0] | add[0] | mul[1] | mul[0]</t>
+          <t>_to_copy[0] | pow[0] | mean[0] | add[0] | _to_copy[0] | mul[0](param:weight)</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr"/>
@@ -3118,9 +3082,21 @@
           <t>mm[0] | mm[1]</t>
         </is>
       </c>
-      <c r="I47" s="4" t="inlineStr"/>
-      <c r="J47" s="4" t="inlineStr"/>
-      <c r="K47" s="4" t="inlineStr"/>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>[128, 1536]</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>torch.bfloat16</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>mm[0]</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
@@ -3146,7 +3122,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>[1, 128, 1536], [1, 128, 1536], [1, 128, 1536], [1, 128, 1], [1536]</t>
+          <t>[1, 128, 1536], [1, 128, 1536], [1, 128, 1], [1, 128, 1536], [1536]</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
@@ -3156,24 +3132,12 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>_to_copy[0] | pow[0] | mean[0] | add[0] | mul[0]</t>
-        </is>
-      </c>
-      <c r="I48" s="4" t="inlineStr">
-        <is>
-          <t>[1, 128, 1536]</t>
-        </is>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>torch.bfloat16</t>
-        </is>
-      </c>
-      <c r="K48" s="4" t="inlineStr">
-        <is>
-          <t>mul[0]</t>
-        </is>
-      </c>
+          <t>_to_copy[0] | mean[0] | add[0] | _to_copy[0] | mul[0](param:weight)</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr"/>
+      <c r="J48" s="4" t="inlineStr"/>
+      <c r="K48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
@@ -3199,17 +3163,17 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>[128, 1536], [1536, 24576]</t>
+          <t>[128, 1536]</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>torch.bfloat16, torch.bfloat16</t>
+          <t>torch.bfloat16</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>mm[0] | mm[1]</t>
+          <t>mm[0]</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
@@ -3265,21 +3229,9 @@
           <t>transpose[0]</t>
         </is>
       </c>
-      <c r="I50" s="4" t="inlineStr">
-        <is>
-          <t>[1, 128, 128, 192]</t>
-        </is>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>torch.bfloat16</t>
-        </is>
-      </c>
-      <c r="K50" s="4" t="inlineStr">
-        <is>
-          <t>transpose[0]</t>
-        </is>
-      </c>
+      <c r="I50" s="4" t="inlineStr"/>
+      <c r="J50" s="4" t="inlineStr"/>
+      <c r="K50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
@@ -3399,7 +3351,7 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>[1, 128, 512], [1, 128, 512], [512]</t>
+          <t>[1, 128, 512], [1, 128, 1], [512]</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
@@ -3409,7 +3361,7 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>_to_copy[0] | _to_copy[0] | mul[0]</t>
+          <t>_to_copy[0] | add[0] | mul[0](param:weight)</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr"/>
@@ -3440,22 +3392,34 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>[128, 512], [512, 32768]</t>
+          <t>[128, 512]</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>torch.bfloat16, torch.bfloat16</t>
+          <t>torch.bfloat16</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>mm[0] | mm[1]</t>
-        </is>
-      </c>
-      <c r="I54" s="4" t="inlineStr"/>
-      <c r="J54" s="4" t="inlineStr"/>
-      <c r="K54" s="4" t="inlineStr"/>
+          <t>mm[0]</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>[128, 32768]</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>torch.bfloat16</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>mm[0]</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
@@ -3522,34 +3486,22 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>[32], [32], [32], [128, 64]</t>
+          <t>[32], [32], [32], [128, 1], [128, 64]</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>torch.float32, torch.float32, torch.float32, torch.float32</t>
+          <t>torch.float32, torch.float32, torch.float32, torch.float32, torch.float32</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>reciprocal[0] | reciprocal[0] | mul[0] | _to_copy[0]</t>
-        </is>
-      </c>
-      <c r="I56" s="4" t="inlineStr">
-        <is>
-          <t>[128, 64]</t>
-        </is>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>torch.bfloat16</t>
-        </is>
-      </c>
-      <c r="K56" s="4" t="inlineStr">
-        <is>
-          <t>_to_copy[0]</t>
-        </is>
-      </c>
+          <t>reciprocal[0] | div[0] | mul[0] | mul[0] | _to_copy[0]</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr"/>
+      <c r="J56" s="4" t="inlineStr"/>
+      <c r="K56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
@@ -3575,17 +3527,17 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>[128, 64], [1, 128], [128, 64], [1, 1, 128, 64], [1, 128, 128, 128], [1, 128, 128, 64], [1, 128, 128, 128], [1, 128, 128, 128], [1, 1, 128, 128], [1, 128, 128, 128]</t>
+          <t>[128, 64], [1, 128], [128, 64], [1, 1, 128, 64], [1, 1, 128, 64], [1, 128, 128, 128], [1, 128, 128, 128], [1, 1, 128, 128]</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>torch.bfloat16, torch.int64, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.float32, torch.float32</t>
+          <t>torch.bfloat16, torch.int64, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.float32</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>index[0] | index[1] | index[0] | mul[0] | copy_[1] | copy_[1] | copy_[1] | mul[0] | add[1] | _softmax[0]</t>
+          <t>index[0] | index[1] | index[0] | mul[0] | new_empty[0] | copy_[1] | mul[0] | add[1]</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
@@ -3628,17 +3580,17 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>[128, 16384], [16384, 7168]</t>
+          <t>[128, 16384]</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>torch.bfloat16, torch.bfloat16</t>
+          <t>torch.bfloat16</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>mm[0] | mm[1]</t>
+          <t>mm[0]</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr"/>
@@ -3722,7 +3674,7 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>[1, 128, 7168], [1, 128, 7168], [1, 128, 1], [1, 128, 7168], [7168]</t>
+          <t>[1, 128, 7168], [1, 128, 7168], [1, 128, 1], [1, 128, 1], [7168]</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
@@ -3732,7 +3684,7 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>_to_copy[0] | mean[0] | add[0] | _to_copy[0] | mul[0]</t>
+          <t>_to_copy[0] | pow[0] | add[0] | mul[1] | mul[0](param:weight)</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr"/>
@@ -3922,17 +3874,17 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>[1, 128, 18432], [1, 128, 18432]</t>
+          <t>[1, 128, 18432]</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>torch.bfloat16, torch.bfloat16</t>
+          <t>torch.bfloat16</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>mul[0] | mul[1]</t>
+          <t>mul[1]</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr"/>
@@ -4029,21 +3981,9 @@
           <t>add[0] | add[1]</t>
         </is>
       </c>
-      <c r="I66" s="4" t="inlineStr">
-        <is>
-          <t>[1, 128, 7168]</t>
-        </is>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>torch.bfloat16</t>
-        </is>
-      </c>
-      <c r="K66" s="4" t="inlineStr">
-        <is>
-          <t>add[0]</t>
-        </is>
-      </c>
+      <c r="I66" s="4" t="inlineStr"/>
+      <c r="J66" s="4" t="inlineStr"/>
+      <c r="K66" s="4" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
@@ -4069,17 +4009,17 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>[1, 128, 7168], [1, 128, 7168], [1, 128, 7168], [1, 128, 1], [1, 128, 7168], [7168]</t>
+          <t>[1, 128, 7168], [1, 128, 7168], [1, 128, 1], [1, 128, 1], [7168]</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>torch.bfloat16, torch.float32, torch.float32, torch.float32, torch.float32, torch.bfloat16</t>
+          <t>torch.bfloat16, torch.float32, torch.float32, torch.float32, torch.bfloat16</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>_to_copy[0] | pow[0] | mean[0] | add[0] | _to_copy[0] | mul[0]</t>
+          <t>_to_copy[0] | pow[0] | add[0] | mul[1] | mul[0](param:weight)</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr"/>
@@ -4123,21 +4063,9 @@
           <t>mm[0] | mm[1]</t>
         </is>
       </c>
-      <c r="I68" s="4" t="inlineStr">
-        <is>
-          <t>[128, 1536]</t>
-        </is>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>torch.bfloat16</t>
-        </is>
-      </c>
-      <c r="K68" s="4" t="inlineStr">
-        <is>
-          <t>mm[0]</t>
-        </is>
-      </c>
+      <c r="I68" s="4" t="inlineStr"/>
+      <c r="J68" s="4" t="inlineStr"/>
+      <c r="K68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
@@ -4163,17 +4091,17 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>[1, 128, 1536], [1, 128, 1536], [1, 128, 1536], [1, 128, 1], [1, 128, 1536], [1536]</t>
+          <t>[1, 128, 1536], [1, 128, 1536], [1, 128, 1536], [1, 128, 1], [1536]</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>torch.bfloat16, torch.float32, torch.float32, torch.float32, torch.float32, torch.bfloat16</t>
+          <t>torch.bfloat16, torch.float32, torch.float32, torch.float32, torch.bfloat16</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>_to_copy[0] | pow[0] | mean[0] | add[0] | _to_copy[0] | mul[0]</t>
+          <t>_to_copy[0] | pow[0] | mean[0] | add[0] | mul[0](param:weight)</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr"/>
@@ -4390,7 +4318,7 @@
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>_to_copy[0] | pow[0] | add[0] | mul[0]</t>
+          <t>_to_copy[0] | pow[0] | add[0] | mul[0](param:weight)</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr"/>
@@ -4568,17 +4496,17 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>[128, 64], [1, 128], [128, 64], [1, 1, 128, 64], [1, 1, 128, 64], [1, 128, 128, 128], [1, 128, 128, 128], [1, 1, 128, 128]</t>
+          <t>[128, 64], [1, 128], [128, 64], [1, 1, 128, 64], [1, 1, 128, 64], [1, 128, 128, 128], [1, 128, 128, 128], [1, 128, 128, 128], [1, 1, 128, 128]</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>torch.bfloat16, torch.int64, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.float32</t>
+          <t>torch.bfloat16, torch.int64, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.float32</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>index[0] | index[1] | index[0] | mul[0] | new_empty[0] | copy_[1] | mul[0] | add[1]</t>
+          <t>index[0] | index[1] | index[0] | mul[0] | new_empty[0] | copy_[1] | copy_[1] | mul[0] | add[1]</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
@@ -4737,7 +4665,7 @@
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>_to_copy[0] | pow[0] | mul[1] | mul[0]</t>
+          <t>_to_copy[0] | pow[0] | add[0] | mul[0](param:weight)</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr"/>
@@ -4768,17 +4696,17 @@
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>[128, 7168], [256, 7168], [7168, 256], [128, 256], [128, 256], [128, 1], [128, 8]</t>
+          <t>[128, 7168], [256, 7168], [128, 7168], [7168, 256], [128, 8], [128, 256], [128, 8], [128, 8]</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>torch.bfloat16, torch.bfloat16, torch.float32, torch.float32, torch.bool, torch.float32, torch.float32</t>
+          <t>torch.bfloat16, torch.bfloat16, torch.float32, torch.float32, torch.float32, torch.bool, torch.float32, torch.float32</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>_to_copy[0] | _to_copy[0] | mm[1] | sigmoid[0] | masked_fill[1] | div[1] | mul[0]</t>
+          <t>_to_copy[0] | _to_copy[0](param:weight) | mm[0] | mm[1] | topk[0] | masked_fill[1](const) | sum[0] | mul[0]</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
@@ -5482,34 +5410,22 @@
       <c r="E96" s="4" t="inlineStr"/>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>[1, 128, 7168], [1, 128, 1], [1, 128, 1], [7168]</t>
+          <t>[1, 128, 7168], [1, 128, 7168], [1, 128, 1], [7168], [1, 128, 7168]</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>torch.float32, torch.float32, torch.float32, torch.bfloat16</t>
+          <t>torch.float32, torch.float32, torch.float32, torch.bfloat16, torch.float32</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>pow[0] | rsqrt[0] | mul[1] | mul[0]</t>
-        </is>
-      </c>
-      <c r="I96" s="4" t="inlineStr">
-        <is>
-          <t>[1, 128, 7168]</t>
-        </is>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>torch.float32</t>
-        </is>
-      </c>
-      <c r="K96" s="4" t="inlineStr">
-        <is>
-          <t>mul[0]</t>
-        </is>
-      </c>
+          <t>pow[0] | mean[0] | rsqrt[0] | mul[0](param:weight) | mul[1]</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr"/>
+      <c r="J96" s="4" t="inlineStr"/>
+      <c r="K96" s="4" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="n">
@@ -26351,17 +26267,17 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>[1, 128, 7168], [1, 128, 7168], [1, 128, 1], [1, 128, 7168], [7168]</t>
+          <t>[1, 128, 7168], [1, 128, 7168], [1, 128, 1], [7168]</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>torch.bfloat16, torch.float32, torch.float32, torch.float32, torch.bfloat16</t>
+          <t>torch.bfloat16, torch.float32, torch.float32, torch.bfloat16</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>_to_copy[0] | pow[0] | add[0] | _to_copy[0] | mul[0]</t>
+          <t>_to_copy[0] | pow[0] | add[0] | mul[0](param:weight)</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr"/>
@@ -26397,22 +26313,34 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>[32], [32], [32], [128, 1], [128, 64]</t>
+          <t>[32], [32], [32], [128, 1], [128, 64], [128, 64]</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>torch.float32, torch.float32, torch.float32, torch.float32, torch.float32</t>
+          <t>torch.float32, torch.float32, torch.float32, torch.float32, torch.float32, torch.float32</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>reciprocal[0] | div[0] | mul[0] | mul[0] | _to_copy[0]</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr"/>
-      <c r="K3" s="4" t="inlineStr"/>
-      <c r="L3" s="4" t="inlineStr"/>
+          <t>reciprocal[0] | div[0] | mul[0] | mul[0] | cos[0] | _to_copy[0]</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>[128, 64]</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>torch.bfloat16</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>_to_copy[0]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -26443,32 +26371,32 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>[128, 64], [1, 128], [128, 64], [1, 1, 128, 64], [1, 1, 128, 64], [1, 128, 128, 128], [1, 128, 128, 128], [1, 128, 128, 128], [1, 1, 128, 128], [128, 128, 128]</t>
+          <t>[128, 64], [1, 128], [128, 64], [1, 1, 128, 64], [1, 1, 128, 64], [1, 128, 128, 128], [1, 128, 128, 128], [1, 1, 128, 128], [128, 128, 128]</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>torch.bfloat16, torch.int64, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.float32, torch.bfloat16</t>
+          <t>torch.bfloat16, torch.int64, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.bfloat16, torch.float32, torch.bfloat16</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>index[0] | index[1] | index[0] | mul[0] | new_empty[0] | copy_[1] | copy_[1] | mul[0] | add[1] | bmm[1]</t>
+          <t>index[0] | index[1] | index[0] | mul[0] | new_empty[0] | copy_[1] | mul[0] | add[1] | bmm[1]</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>[1, 128, 128, 192], [1, 128, 128, 128], [128, 128, 128]</t>
+          <t>[1, 128, 128, 128], [128, 128, 128]</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>torch.bfloat16, torch.bfloat16, torch.bfloat16</t>
+          <t>torch.bfloat16, torch.bfloat16</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>new_empty[0] | _to_copy[0] | bmm[0]</t>
+          <t>_to_copy[0] | bmm[0]</t>
         </is>
       </c>
     </row>
@@ -26501,17 +26429,17 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>[1, 1, 128, 128], [1, 1, 128, 128], [1, 1, 128, 128]</t>
+          <t>[1, 1, 128, 128], [1, 1, 128, 128]</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>torch.float32, torch.float32, torch.bool</t>
+          <t>torch.float32, torch.float32</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>rsub[0] | _to_copy[0] | masked_fill[1]</t>
+          <t>rsub[0] | _to_copy[0]</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -26559,17 +26487,17 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>[128, 7168], [256, 7168], [7168, 256], [128, 256], [128, 256], [128, 1], [128, 8]</t>
+          <t>[128, 7168], [256, 7168], [128, 7168], [7168, 256], [128, 8], [128, 256], [128, 8], [128, 8]</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>torch.bfloat16, torch.bfloat16, torch.float32, torch.float32, torch.bool, torch.float32, torch.float32</t>
+          <t>torch.bfloat16, torch.bfloat16, torch.float32, torch.float32, torch.float32, torch.bool, torch.float32, torch.float32</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>_to_copy[0] | _to_copy[0] | mm[1] | sigmoid[0] | masked_fill[1] | div[1] | mul[0]</t>
+          <t>_to_copy[0] | _to_copy[0](param:weight) | mm[0] | mm[1] | topk[0] | masked_fill[1](const) | sum[0] | mul[0]</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
